--- a/Wasser/Photometrische Messung (Stefan)/3 Auswertung Photometrie.xlsx
+++ b/Wasser/Photometrische Messung (Stefan)/3 Auswertung Photometrie.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\Photometrische Messung (Stefan)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0C6AF8-268B-413D-8063-FBADAB4F566B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7199CADE-C578-420E-9594-CCACFC2B4822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="134">
   <si>
     <t>sample</t>
   </si>
@@ -420,6 +420,30 @@
   <si>
     <t>Mittelwerte je Logger</t>
   </si>
+  <si>
+    <t>Fläche</t>
+  </si>
+  <si>
+    <t>Molgewicht  NO3</t>
+  </si>
+  <si>
+    <t>NH₄⁺ (SD)</t>
+  </si>
+  <si>
+    <t>PO₄³⁻ (SD)</t>
+  </si>
+  <si>
+    <t>NO₃⁻ (SD)</t>
+  </si>
+  <si>
+    <t>NH₄⁺ [mg/L]</t>
+  </si>
+  <si>
+    <t>PO₄³⁻ [mg/L]</t>
+  </si>
+  <si>
+    <t>NO₃⁻ [mg/L]</t>
+  </si>
 </sst>
 </file>
 
@@ -427,7 +451,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1517,7 +1541,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1584,43 +1608,16 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1635,6 +1632,54 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1647,34 +1692,19 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1683,14 +1713,37 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="33" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14695,16 +14748,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -14910,14 +14963,14 @@
       <c r="B55" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C55" s="52">
+      <c r="C55" s="77">
         <v>1</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="53">
+      <c r="D55" s="77"/>
+      <c r="E55" s="68">
         <v>0</v>
       </c>
-      <c r="F55" s="54"/>
+      <c r="F55" s="69"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -14929,15 +14982,15 @@
       <c r="B56" s="6">
         <v>1.6E-2</v>
       </c>
-      <c r="C56" s="49">
+      <c r="C56" s="76">
         <v>2.5</v>
       </c>
-      <c r="D56" s="49"/>
-      <c r="E56" s="55">
+      <c r="D56" s="76"/>
+      <c r="E56" s="57">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-4.3010752688172157E-2</v>
       </c>
-      <c r="F56" s="56"/>
+      <c r="F56" s="58"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -14949,15 +15002,15 @@
       <c r="B57" s="6">
         <v>0.04</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="76">
         <v>5</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="55">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.5376344086021505</v>
       </c>
-      <c r="F57" s="56"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -14978,10 +15031,10 @@
       <c r="B58" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="76">
         <v>10</v>
       </c>
-      <c r="D58" s="49"/>
+      <c r="D58" s="76"/>
       <c r="E58" s="50">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.2688172043010768</v>
@@ -15007,10 +15060,10 @@
       <c r="B59" s="6">
         <v>0.22800000000000001</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="76">
         <v>25</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="76"/>
       <c r="E59" s="50">
         <f t="shared" si="1"/>
         <v>22.752688172043015</v>
@@ -15027,10 +15080,10 @@
       <c r="B60" s="6">
         <v>0.54300000000000004</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="76">
         <v>50</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="76"/>
       <c r="E60" s="50">
         <f t="shared" si="1"/>
         <v>56.62365591397851</v>
@@ -15056,10 +15109,10 @@
       <c r="B61" s="6">
         <v>0.98199999999999998</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="76">
         <v>100</v>
       </c>
-      <c r="D61" s="49"/>
+      <c r="D61" s="76"/>
       <c r="E61" s="50">
         <f t="shared" si="1"/>
         <v>103.82795698924733</v>
@@ -15085,15 +15138,15 @@
       <c r="B62" s="8">
         <v>1.8460000000000001</v>
       </c>
-      <c r="C62" s="61">
+      <c r="C62" s="52">
         <v>200</v>
       </c>
-      <c r="D62" s="62"/>
-      <c r="E62" s="63">
+      <c r="D62" s="53"/>
+      <c r="E62" s="54">
         <f t="shared" si="1"/>
         <v>196.73118279569894</v>
       </c>
-      <c r="F62" s="64"/>
+      <c r="F62" s="55"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -15114,12 +15167,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="65"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="67">
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74">
         <v>0</v>
       </c>
-      <c r="F63" s="68"/>
+      <c r="F63" s="75"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -15140,12 +15193,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="59"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="55">
+      <c r="C64" s="48"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="57">
         <v>0</v>
       </c>
-      <c r="F64" s="56"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15166,12 +15219,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="59"/>
-      <c r="D65" s="60"/>
-      <c r="E65" s="55">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="57">
         <v>0</v>
       </c>
-      <c r="F65" s="56"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15192,12 +15245,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="59"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="55">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <v>0</v>
       </c>
-      <c r="F66" s="56"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15218,13 +15271,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="55">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="56"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -15245,13 +15298,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="55">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="56"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -15272,13 +15325,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="55">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -15299,13 +15352,13 @@
       <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="61"/>
-      <c r="D70" s="69"/>
-      <c r="E70" s="57">
+      <c r="C70" s="52"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="60">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="58"/>
+      <c r="F70" s="61"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -15390,11 +15443,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="53">
+      <c r="E101" s="68">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="54"/>
+      <c r="F101" s="69"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -15419,11 +15472,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="55">
+      <c r="E102" s="57">
         <f t="shared" ref="E102:E106" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="56"/>
+      <c r="F102" s="58"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -15448,11 +15501,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="55">
+      <c r="E103" s="57">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="56"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -15477,11 +15530,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="55">
+      <c r="E104" s="57">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="56"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -15506,11 +15559,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="55">
+      <c r="E105" s="57">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="56"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -15535,11 +15588,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="57">
+      <c r="E106" s="60">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="58"/>
+      <c r="F106" s="61"/>
       <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -15560,13 +15613,13 @@
       <c r="B107" s="4">
         <v>0</v>
       </c>
-      <c r="C107" s="70"/>
+      <c r="C107" s="62"/>
       <c r="D107" s="71"/>
-      <c r="E107" s="53">
+      <c r="E107" s="68">
         <f t="shared" ref="E107" si="12">(B107+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="54"/>
+      <c r="F107" s="69"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15587,13 +15640,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="59"/>
-      <c r="D108" s="60"/>
-      <c r="E108" s="55">
+      <c r="C108" s="48"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="57">
         <f t="shared" ref="E108:E114" si="13">(B108+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="56"/>
+      <c r="F108" s="58"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="14">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15614,13 +15667,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="59"/>
-      <c r="D109" s="60"/>
-      <c r="E109" s="55">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="56"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15641,13 +15694,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="59"/>
-      <c r="D110" s="60"/>
-      <c r="E110" s="55">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="56"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15668,13 +15721,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="59"/>
-      <c r="D111" s="60"/>
-      <c r="E111" s="55">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="13"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="56"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>9.2647058823529408E-7</v>
@@ -15695,13 +15748,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="59"/>
-      <c r="D112" s="60"/>
-      <c r="E112" s="55">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="13"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="56"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>6.8137254901960776E-7</v>
@@ -15722,13 +15775,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="59"/>
-      <c r="D113" s="60"/>
-      <c r="E113" s="55">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="13"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="56"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>2.1519607843137253E-6</v>
@@ -15749,13 +15802,13 @@
       <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="61"/>
-      <c r="D114" s="69"/>
-      <c r="E114" s="57">
+      <c r="C114" s="52"/>
+      <c r="D114" s="59"/>
+      <c r="E114" s="60">
         <f t="shared" si="13"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="58"/>
+      <c r="F114" s="61"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>5.3431372549019611E-7</v>
@@ -15771,7 +15824,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -15787,16 +15840,16 @@
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="48" t="s">
+      <c r="A120" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="48"/>
-      <c r="C120" s="48"/>
-      <c r="D120" s="48"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="48"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="70"/>
+      <c r="H120" s="70"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I121" s="16" t="s">
@@ -15842,14 +15895,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="70">
+      <c r="C123" s="62">
         <v>2.5</v>
       </c>
-      <c r="D123" s="72"/>
-      <c r="E123" s="53">
+      <c r="D123" s="63"/>
+      <c r="E123" s="68">
         <v>0</v>
       </c>
-      <c r="F123" s="54"/>
+      <c r="F123" s="69"/>
       <c r="G123" s="35"/>
       <c r="I123" s="16">
         <f t="shared" ref="I123:I130" si="17">C123/1000000</f>
@@ -15871,10 +15924,10 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="76">
+      <c r="C124" s="66">
         <v>5</v>
       </c>
-      <c r="D124" s="77"/>
+      <c r="D124" s="67"/>
       <c r="E124" s="50">
         <f t="shared" ref="E124:E130" si="18">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
@@ -15901,10 +15954,10 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="59">
+      <c r="C125" s="48">
         <v>10</v>
       </c>
-      <c r="D125" s="75"/>
+      <c r="D125" s="49"/>
       <c r="E125" s="50">
         <f t="shared" si="18"/>
         <v>7.7368421052631584</v>
@@ -15931,10 +15984,10 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="59">
+      <c r="C126" s="48">
         <v>25</v>
       </c>
-      <c r="D126" s="75"/>
+      <c r="D126" s="49"/>
       <c r="E126" s="50">
         <f t="shared" si="18"/>
         <v>25.105263157894736</v>
@@ -15961,10 +16014,10 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="59">
+      <c r="C127" s="48">
         <v>50</v>
       </c>
-      <c r="D127" s="75"/>
+      <c r="D127" s="49"/>
       <c r="E127" s="50">
         <f t="shared" si="18"/>
         <v>47.210526315789473</v>
@@ -15991,10 +16044,10 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="59">
+      <c r="C128" s="48">
         <v>100</v>
       </c>
-      <c r="D128" s="75"/>
+      <c r="D128" s="49"/>
       <c r="E128" s="50">
         <f t="shared" si="18"/>
         <v>95.631578947368425</v>
@@ -16021,10 +16074,10 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="59">
+      <c r="C129" s="48">
         <v>200</v>
       </c>
-      <c r="D129" s="75"/>
+      <c r="D129" s="49"/>
       <c r="E129" s="50">
         <f t="shared" si="18"/>
         <v>200.89473684210526</v>
@@ -16051,15 +16104,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="61">
+      <c r="C130" s="52">
         <v>500</v>
       </c>
-      <c r="D130" s="62"/>
-      <c r="E130" s="63">
+      <c r="D130" s="53"/>
+      <c r="E130" s="54">
         <f t="shared" si="18"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="64"/>
+      <c r="F130" s="55"/>
       <c r="G130" s="35"/>
       <c r="I130" s="19">
         <f t="shared" si="17"/>
@@ -16081,13 +16134,13 @@
       <c r="B131" s="4">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="70"/>
-      <c r="D131" s="72"/>
-      <c r="E131" s="73">
+      <c r="C131" s="62"/>
+      <c r="D131" s="63"/>
+      <c r="E131" s="64">
         <f t="shared" ref="E131:E138" si="21">(B131+0.0067)/0.0019</f>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="74"/>
+      <c r="F131" s="65"/>
       <c r="G131" s="35"/>
       <c r="I131" s="18">
         <f>E131/1000000</f>
@@ -16109,8 +16162,8 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="59"/>
-      <c r="D132" s="75"/>
+      <c r="C132" s="48"/>
+      <c r="D132" s="49"/>
       <c r="E132" s="50">
         <v>0</v>
       </c>
@@ -16136,8 +16189,8 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="59"/>
-      <c r="D133" s="75"/>
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
       <c r="E133" s="50">
         <v>0</v>
       </c>
@@ -16163,8 +16216,8 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="59"/>
-      <c r="D134" s="75"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
       <c r="E134" s="50">
         <v>0</v>
       </c>
@@ -16190,8 +16243,8 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="59"/>
-      <c r="D135" s="75"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="50">
         <v>0</v>
       </c>
@@ -16217,8 +16270,8 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="75"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
       <c r="E136" s="50">
         <f t="shared" si="21"/>
         <v>13</v>
@@ -16245,8 +16298,8 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="59"/>
-      <c r="D137" s="75"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="50">
         <f t="shared" si="21"/>
         <v>18.263157894736842</v>
@@ -16273,13 +16326,13 @@
       <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="61"/>
-      <c r="D138" s="62"/>
-      <c r="E138" s="63">
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="54">
         <f t="shared" si="21"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="64"/>
+      <c r="F138" s="55"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="24"/>
@@ -16296,26 +16349,58 @@
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
     <mergeCell ref="C113:D113"/>
     <mergeCell ref="E113:F113"/>
     <mergeCell ref="C114:D114"/>
@@ -16332,58 +16417,26 @@
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
     <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16406,16 +16459,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -16619,14 +16672,14 @@
         <v>34</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="52">
+      <c r="C55" s="77">
         <v>1</v>
       </c>
-      <c r="D55" s="52"/>
-      <c r="E55" s="53">
+      <c r="D55" s="77"/>
+      <c r="E55" s="68">
         <v>0</v>
       </c>
-      <c r="F55" s="54"/>
+      <c r="F55" s="69"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -16636,15 +16689,15 @@
         <v>35</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="49">
+      <c r="C56" s="76">
         <v>2.5</v>
       </c>
-      <c r="D56" s="49"/>
-      <c r="E56" s="55">
+      <c r="D56" s="76"/>
+      <c r="E56" s="57">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F56" s="56"/>
+      <c r="F56" s="58"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -16656,15 +16709,15 @@
       <c r="B57" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="76">
         <v>5</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="55">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.0000000000000004</v>
       </c>
-      <c r="F57" s="56"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -16685,10 +16738,10 @@
       <c r="B58" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="76">
         <v>10</v>
       </c>
-      <c r="D58" s="49"/>
+      <c r="D58" s="76"/>
       <c r="E58" s="50">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.1612903225806468</v>
@@ -16712,10 +16765,10 @@
         <v>36</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="49">
+      <c r="C59" s="76">
         <v>25</v>
       </c>
-      <c r="D59" s="49"/>
+      <c r="D59" s="76"/>
       <c r="E59" s="50">
         <f t="shared" si="1"/>
         <v>-1.763440860215054</v>
@@ -16732,10 +16785,10 @@
       <c r="B60" s="6">
         <v>0.48499999999999999</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="76">
         <v>50</v>
       </c>
-      <c r="D60" s="49"/>
+      <c r="D60" s="76"/>
       <c r="E60" s="50">
         <f t="shared" si="1"/>
         <v>50.387096774193552</v>
@@ -16761,10 +16814,10 @@
       <c r="B61" s="6">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="76">
         <v>100</v>
       </c>
-      <c r="D61" s="49"/>
+      <c r="D61" s="76"/>
       <c r="E61" s="50">
         <f t="shared" si="1"/>
         <v>102.00000000000001</v>
@@ -16790,15 +16843,15 @@
       <c r="B62" s="8">
         <v>1.8340000000000001</v>
       </c>
-      <c r="C62" s="61">
+      <c r="C62" s="52">
         <v>200</v>
       </c>
-      <c r="D62" s="62"/>
-      <c r="E62" s="63">
+      <c r="D62" s="53"/>
+      <c r="E62" s="54">
         <f t="shared" si="1"/>
         <v>195.44086021505379</v>
       </c>
-      <c r="F62" s="64"/>
+      <c r="F62" s="55"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -16819,12 +16872,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="65"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="67">
+      <c r="C63" s="72"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="74">
         <v>0</v>
       </c>
-      <c r="F63" s="68"/>
+      <c r="F63" s="75"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -16845,12 +16898,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="59"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="55">
+      <c r="C64" s="48"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="57">
         <v>0</v>
       </c>
-      <c r="F64" s="56"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16871,12 +16924,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="59"/>
-      <c r="D65" s="60"/>
-      <c r="E65" s="55">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="57">
         <v>0</v>
       </c>
-      <c r="F65" s="56"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16897,12 +16950,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="59"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="55">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <v>0</v>
       </c>
-      <c r="F66" s="56"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16923,13 +16976,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="55">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="56"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -16950,13 +17003,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="55">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="56"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -16977,13 +17030,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="55">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -17004,13 +17057,13 @@
       <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="61"/>
-      <c r="D70" s="69"/>
-      <c r="E70" s="57">
+      <c r="C70" s="52"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="60">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="58"/>
+      <c r="F70" s="61"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -17095,11 +17148,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="53">
+      <c r="E101" s="68">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="54"/>
+      <c r="F101" s="69"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -17124,11 +17177,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="55">
+      <c r="E102" s="57">
         <f t="shared" ref="E102:E114" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="56"/>
+      <c r="F102" s="58"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -17153,11 +17206,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="55">
+      <c r="E103" s="57">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="56"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -17182,11 +17235,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="55">
+      <c r="E104" s="57">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="56"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -17211,11 +17264,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="55">
+      <c r="E105" s="57">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="56"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -17240,11 +17293,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="57">
+      <c r="E106" s="60">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="58"/>
+      <c r="F106" s="61"/>
       <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -17265,13 +17318,13 @@
       <c r="B107" s="9">
         <v>0</v>
       </c>
-      <c r="C107" s="65"/>
-      <c r="D107" s="66"/>
-      <c r="E107" s="67">
+      <c r="C107" s="72"/>
+      <c r="D107" s="73"/>
+      <c r="E107" s="74">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="68"/>
+      <c r="F107" s="75"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -17292,13 +17345,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="59"/>
-      <c r="D108" s="60"/>
-      <c r="E108" s="55">
+      <c r="C108" s="48"/>
+      <c r="D108" s="56"/>
+      <c r="E108" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="56"/>
+      <c r="F108" s="58"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="12">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -17319,13 +17372,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="59"/>
-      <c r="D109" s="60"/>
-      <c r="E109" s="55">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="56"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -17346,13 +17399,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="59"/>
-      <c r="D110" s="60"/>
-      <c r="E110" s="55">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="56"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -17373,13 +17426,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="59"/>
-      <c r="D111" s="60"/>
-      <c r="E111" s="55">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="10"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="56"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="12"/>
         <v>9.2647058823529408E-7</v>
@@ -17400,13 +17453,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="59"/>
-      <c r="D112" s="60"/>
-      <c r="E112" s="55">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="10"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="56"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="12"/>
         <v>6.8137254901960776E-7</v>
@@ -17427,13 +17480,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="59"/>
-      <c r="D113" s="60"/>
-      <c r="E113" s="55">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="10"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="56"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="12"/>
         <v>2.1519607843137253E-6</v>
@@ -17454,13 +17507,13 @@
       <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="61"/>
-      <c r="D114" s="69"/>
-      <c r="E114" s="57">
+      <c r="C114" s="52"/>
+      <c r="D114" s="59"/>
+      <c r="E114" s="60">
         <f t="shared" si="10"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="58"/>
+      <c r="F114" s="61"/>
       <c r="I114" s="18">
         <f t="shared" si="12"/>
         <v>5.3431372549019611E-7</v>
@@ -17476,7 +17529,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -17492,16 +17545,16 @@
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="48" t="s">
+      <c r="A120" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="48"/>
-      <c r="C120" s="48"/>
-      <c r="D120" s="48"/>
-      <c r="E120" s="48"/>
-      <c r="F120" s="48"/>
-      <c r="G120" s="48"/>
-      <c r="H120" s="48"/>
+      <c r="B120" s="70"/>
+      <c r="C120" s="70"/>
+      <c r="D120" s="70"/>
+      <c r="E120" s="70"/>
+      <c r="F120" s="70"/>
+      <c r="G120" s="70"/>
+      <c r="H120" s="70"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I121" s="16" t="s">
@@ -17547,14 +17600,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="70">
+      <c r="C123" s="62">
         <v>2.5</v>
       </c>
-      <c r="D123" s="72"/>
-      <c r="E123" s="53">
+      <c r="D123" s="63"/>
+      <c r="E123" s="68">
         <v>0</v>
       </c>
-      <c r="F123" s="54"/>
+      <c r="F123" s="69"/>
       <c r="G123" s="35"/>
       <c r="I123" s="16">
         <f t="shared" ref="I123:I130" si="15">C123/1000000</f>
@@ -17576,10 +17629,10 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="76">
+      <c r="C124" s="66">
         <v>5</v>
       </c>
-      <c r="D124" s="77"/>
+      <c r="D124" s="67"/>
       <c r="E124" s="50">
         <f t="shared" ref="E124:E138" si="16">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
@@ -17606,10 +17659,10 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="59">
+      <c r="C125" s="48">
         <v>10</v>
       </c>
-      <c r="D125" s="75"/>
+      <c r="D125" s="49"/>
       <c r="E125" s="50">
         <f t="shared" si="16"/>
         <v>7.7368421052631584</v>
@@ -17636,10 +17689,10 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="59">
+      <c r="C126" s="48">
         <v>25</v>
       </c>
-      <c r="D126" s="75"/>
+      <c r="D126" s="49"/>
       <c r="E126" s="50">
         <f t="shared" si="16"/>
         <v>25.105263157894736</v>
@@ -17666,10 +17719,10 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="59">
+      <c r="C127" s="48">
         <v>50</v>
       </c>
-      <c r="D127" s="75"/>
+      <c r="D127" s="49"/>
       <c r="E127" s="50">
         <f t="shared" si="16"/>
         <v>47.210526315789473</v>
@@ -17696,10 +17749,10 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="59">
+      <c r="C128" s="48">
         <v>100</v>
       </c>
-      <c r="D128" s="75"/>
+      <c r="D128" s="49"/>
       <c r="E128" s="50">
         <f t="shared" si="16"/>
         <v>95.631578947368425</v>
@@ -17726,10 +17779,10 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="59">
+      <c r="C129" s="48">
         <v>200</v>
       </c>
-      <c r="D129" s="75"/>
+      <c r="D129" s="49"/>
       <c r="E129" s="50">
         <f t="shared" si="16"/>
         <v>200.89473684210526</v>
@@ -17756,15 +17809,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="61">
+      <c r="C130" s="52">
         <v>500</v>
       </c>
-      <c r="D130" s="62"/>
-      <c r="E130" s="63">
+      <c r="D130" s="53"/>
+      <c r="E130" s="54">
         <f t="shared" si="16"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="64"/>
+      <c r="F130" s="55"/>
       <c r="G130" s="35"/>
       <c r="I130" s="19">
         <f t="shared" si="15"/>
@@ -17786,13 +17839,13 @@
       <c r="B131" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="65"/>
+      <c r="C131" s="72"/>
       <c r="D131" s="78"/>
-      <c r="E131" s="73">
+      <c r="E131" s="64">
         <f t="shared" si="16"/>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="74"/>
+      <c r="F131" s="65"/>
       <c r="G131" s="35"/>
       <c r="I131" s="18">
         <f>E131/1000000</f>
@@ -17814,8 +17867,8 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="59"/>
-      <c r="D132" s="75"/>
+      <c r="C132" s="48"/>
+      <c r="D132" s="49"/>
       <c r="E132" s="50">
         <v>0</v>
       </c>
@@ -17841,8 +17894,8 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="59"/>
-      <c r="D133" s="75"/>
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
       <c r="E133" s="50">
         <v>0</v>
       </c>
@@ -17868,8 +17921,8 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="59"/>
-      <c r="D134" s="75"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
       <c r="E134" s="50">
         <v>0</v>
       </c>
@@ -17895,8 +17948,8 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="59"/>
-      <c r="D135" s="75"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="50">
         <v>0</v>
       </c>
@@ -17922,8 +17975,8 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="75"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
       <c r="E136" s="50">
         <f t="shared" si="16"/>
         <v>13</v>
@@ -17950,8 +18003,8 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="59"/>
-      <c r="D137" s="75"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="50">
         <f t="shared" si="16"/>
         <v>18.263157894736842</v>
@@ -17978,13 +18031,13 @@
       <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="61"/>
-      <c r="D138" s="62"/>
-      <c r="E138" s="63">
+      <c r="C138" s="52"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="54">
         <f t="shared" si="16"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="64"/>
+      <c r="F138" s="55"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="21"/>
@@ -18001,32 +18054,55 @@
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
     <mergeCell ref="C112:D112"/>
@@ -18040,55 +18116,32 @@
     <mergeCell ref="E123:F123"/>
     <mergeCell ref="C124:D124"/>
     <mergeCell ref="E124:F124"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -18111,16 +18164,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -18329,14 +18382,14 @@
         <v>34</v>
       </c>
       <c r="B56" s="4"/>
-      <c r="C56" s="52">
+      <c r="C56" s="77">
         <v>1</v>
       </c>
-      <c r="D56" s="52"/>
-      <c r="E56" s="53">
+      <c r="D56" s="77"/>
+      <c r="E56" s="68">
         <v>0</v>
       </c>
-      <c r="F56" s="54"/>
+      <c r="F56" s="69"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -18346,15 +18399,15 @@
         <v>35</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="49">
+      <c r="C57" s="76">
         <v>2.5</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="55">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <f>(B57+0.0048)/0.0096</f>
         <v>0.5</v>
       </c>
-      <c r="F57" s="56"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -18366,15 +18419,15 @@
       <c r="B58" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="76">
         <v>5</v>
       </c>
-      <c r="D58" s="49"/>
-      <c r="E58" s="55">
+      <c r="D58" s="76"/>
+      <c r="E58" s="57">
         <f>(B58+0.0048)/0.0096</f>
         <v>4.25</v>
       </c>
-      <c r="F58" s="56"/>
+      <c r="F58" s="58"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -18395,15 +18448,15 @@
       <c r="B59" s="6">
         <v>0.08</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="76">
         <v>10</v>
       </c>
-      <c r="D59" s="49"/>
-      <c r="E59" s="55">
+      <c r="D59" s="76"/>
+      <c r="E59" s="57">
         <f t="shared" ref="E59:E62" si="0">(B59+0.0048)/0.0096</f>
         <v>8.8333333333333339</v>
       </c>
-      <c r="F59" s="56"/>
+      <c r="F59" s="58"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -18422,15 +18475,15 @@
         <v>36</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="49">
+      <c r="C60" s="76">
         <v>25</v>
       </c>
-      <c r="D60" s="49"/>
-      <c r="E60" s="55">
+      <c r="D60" s="76"/>
+      <c r="E60" s="57">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F60" s="56"/>
+      <c r="F60" s="58"/>
       <c r="H60" s="18"/>
       <c r="I60" s="18"/>
       <c r="J60" s="21"/>
@@ -18442,15 +18495,15 @@
       <c r="B61" s="6">
         <v>0.48399999999999999</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="76">
         <v>50</v>
       </c>
-      <c r="D61" s="49"/>
-      <c r="E61" s="55">
+      <c r="D61" s="76"/>
+      <c r="E61" s="57">
         <f t="shared" si="0"/>
         <v>50.916666666666671</v>
       </c>
-      <c r="F61" s="56"/>
+      <c r="F61" s="58"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -18471,15 +18524,15 @@
       <c r="B62" s="6">
         <v>0.97299999999999998</v>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="76">
         <v>100</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="55">
+      <c r="D62" s="76"/>
+      <c r="E62" s="57">
         <f t="shared" si="0"/>
         <v>101.85416666666667</v>
       </c>
-      <c r="F62" s="56"/>
+      <c r="F62" s="58"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>1E-4</v>
@@ -18500,15 +18553,15 @@
       <c r="B63" s="8">
         <v>1.899</v>
       </c>
-      <c r="C63" s="61">
+      <c r="C63" s="52">
         <v>200</v>
       </c>
-      <c r="D63" s="62"/>
-      <c r="E63" s="57">
+      <c r="D63" s="53"/>
+      <c r="E63" s="60">
         <f t="shared" ref="E63" si="3">(B63+0.0048)/0.0096</f>
         <v>198.3125</v>
       </c>
-      <c r="F63" s="58"/>
+      <c r="F63" s="61"/>
       <c r="H63" s="19">
         <f>C63/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -18529,13 +18582,13 @@
       <c r="B64" s="9">
         <v>1.25</v>
       </c>
-      <c r="C64" s="65"/>
-      <c r="D64" s="66"/>
-      <c r="E64" s="67">
+      <c r="C64" s="72"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="74">
         <f t="shared" ref="E64" si="4">(B64+0.0048)/0.0096</f>
         <v>130.70833333333334</v>
       </c>
-      <c r="F64" s="68"/>
+      <c r="F64" s="75"/>
       <c r="H64" s="18">
         <f t="shared" ref="H64:H71" si="5">E64/1000000</f>
         <v>1.3070833333333334E-4</v>
@@ -18556,13 +18609,13 @@
       <c r="B65" s="6">
         <v>1E-3</v>
       </c>
-      <c r="C65" s="59"/>
-      <c r="D65" s="60"/>
-      <c r="E65" s="67">
+      <c r="C65" s="48"/>
+      <c r="D65" s="56"/>
+      <c r="E65" s="74">
         <f t="shared" ref="E65:E71" si="6">(B65+0.0048)/0.0096</f>
         <v>0.60416666666666663</v>
       </c>
-      <c r="F65" s="68"/>
+      <c r="F65" s="75"/>
       <c r="H65" s="18">
         <f t="shared" si="5"/>
         <v>6.0416666666666667E-7</v>
@@ -18583,13 +18636,13 @@
       <c r="B66" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="59"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="67">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="74">
         <f t="shared" si="6"/>
         <v>1.0208333333333335</v>
       </c>
-      <c r="F66" s="68"/>
+      <c r="F66" s="75"/>
       <c r="H66" s="18">
         <f t="shared" si="5"/>
         <v>1.0208333333333334E-6</v>
@@ -18610,13 +18663,13 @@
       <c r="B67" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="67">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="74">
         <f t="shared" si="6"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="F67" s="68"/>
+      <c r="F67" s="75"/>
       <c r="H67" s="18">
         <f t="shared" si="5"/>
         <v>1.3333333333333332E-6</v>
@@ -18637,13 +18690,13 @@
       <c r="B68" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="67">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="74">
         <f t="shared" si="6"/>
         <v>1.9583333333333335</v>
       </c>
-      <c r="F68" s="68"/>
+      <c r="F68" s="75"/>
       <c r="H68" s="18">
         <f t="shared" si="5"/>
         <v>1.9583333333333334E-6</v>
@@ -18664,13 +18717,13 @@
       <c r="B69" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="67">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="74">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F69" s="68"/>
+      <c r="F69" s="75"/>
       <c r="H69" s="18">
         <f t="shared" si="5"/>
         <v>3.0000000000000001E-6</v>
@@ -18691,13 +18744,13 @@
       <c r="B70" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C70" s="59"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="67">
+      <c r="C70" s="48"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="74">
         <f t="shared" si="6"/>
         <v>4.7708333333333339</v>
       </c>
-      <c r="F70" s="68"/>
+      <c r="F70" s="75"/>
       <c r="H70" s="18">
         <f t="shared" si="5"/>
         <v>4.7708333333333335E-6</v>
@@ -18718,13 +18771,13 @@
       <c r="B71" s="8">
         <v>0.311</v>
       </c>
-      <c r="C71" s="61"/>
-      <c r="D71" s="69"/>
-      <c r="E71" s="79">
+      <c r="C71" s="52"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="81">
         <f t="shared" si="6"/>
         <v>32.895833333333336</v>
       </c>
-      <c r="F71" s="80"/>
+      <c r="F71" s="82"/>
       <c r="H71" s="18">
         <f t="shared" si="5"/>
         <v>3.2895833333333338E-5</v>
@@ -18809,11 +18862,11 @@
         <v>0.5</v>
       </c>
       <c r="D102" s="11"/>
-      <c r="E102" s="53">
+      <c r="E102" s="68">
         <f>(B102+0.001)/0.0211</f>
         <v>0.56872037914691942</v>
       </c>
-      <c r="F102" s="54"/>
+      <c r="F102" s="69"/>
       <c r="I102" s="16">
         <f t="shared" ref="I102:I107" si="9">C102/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -18838,11 +18891,11 @@
         <v>1</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="55">
+      <c r="E103" s="57">
         <f t="shared" ref="E103:E107" si="11">(B103+0.001)/0.0211</f>
         <v>1.0426540284360191</v>
       </c>
-      <c r="F103" s="56"/>
+      <c r="F103" s="58"/>
       <c r="I103" s="18">
         <f t="shared" si="9"/>
         <v>9.9999999999999995E-7</v>
@@ -18867,11 +18920,11 @@
         <v>5</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="55">
+      <c r="E104" s="57">
         <f t="shared" si="11"/>
         <v>5.0236966824644549</v>
       </c>
-      <c r="F104" s="56"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000004E-6</v>
@@ -18896,11 +18949,11 @@
         <v>10</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="55">
+      <c r="E105" s="57">
         <f t="shared" si="11"/>
         <v>10.284360189573459</v>
       </c>
-      <c r="F105" s="56"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="9"/>
         <v>1.0000000000000001E-5</v>
@@ -18925,11 +18978,11 @@
         <v>25</v>
       </c>
       <c r="D106" s="33"/>
-      <c r="E106" s="55">
+      <c r="E106" s="57">
         <f t="shared" si="11"/>
         <v>24.976303317535546</v>
       </c>
-      <c r="F106" s="56"/>
+      <c r="F106" s="58"/>
       <c r="I106" s="19">
         <f t="shared" si="9"/>
         <v>2.5000000000000001E-5</v>
@@ -18954,11 +19007,11 @@
         <v>50</v>
       </c>
       <c r="D107" s="15"/>
-      <c r="E107" s="57">
+      <c r="E107" s="60">
         <f t="shared" si="11"/>
         <v>78.436018957345965</v>
       </c>
-      <c r="F107" s="58"/>
+      <c r="F107" s="61"/>
       <c r="I107" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000002E-5</v>
@@ -18979,13 +19032,13 @@
       <c r="B108" s="9">
         <v>0</v>
       </c>
-      <c r="C108" s="65"/>
-      <c r="D108" s="66"/>
-      <c r="E108" s="67">
+      <c r="C108" s="72"/>
+      <c r="D108" s="73"/>
+      <c r="E108" s="74">
         <f t="shared" ref="E108:E115" si="13">(B108+0.001)/0.0211</f>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F108" s="68"/>
+      <c r="F108" s="75"/>
       <c r="I108" s="18">
         <f>E108/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -19006,13 +19059,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="59"/>
-      <c r="D109" s="60"/>
-      <c r="E109" s="55">
+      <c r="C109" s="48"/>
+      <c r="D109" s="56"/>
+      <c r="E109" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F109" s="56"/>
+      <c r="F109" s="58"/>
       <c r="I109" s="18">
         <f t="shared" ref="I109:I115" si="14">E109/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -19033,13 +19086,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="59"/>
-      <c r="D110" s="60"/>
-      <c r="E110" s="55">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F110" s="56"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -19060,13 +19113,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="59"/>
-      <c r="D111" s="60"/>
-      <c r="E111" s="55">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F111" s="56"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -19087,13 +19140,13 @@
       <c r="B112" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C112" s="59"/>
-      <c r="D112" s="60"/>
-      <c r="E112" s="55">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="13"/>
         <v>0.71090047393364919</v>
       </c>
-      <c r="F112" s="56"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>7.1090047393364923E-7</v>
@@ -19114,13 +19167,13 @@
       <c r="B113" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C113" s="59"/>
-      <c r="D113" s="60"/>
-      <c r="E113" s="55">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="13"/>
         <v>0.47393364928909942</v>
       </c>
-      <c r="F113" s="56"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909945E-7</v>
@@ -19141,13 +19194,13 @@
       <c r="B114" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C114" s="59"/>
-      <c r="D114" s="60"/>
-      <c r="E114" s="55">
+      <c r="C114" s="48"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="57">
         <f t="shared" si="13"/>
         <v>1.8957345971563981</v>
       </c>
-      <c r="F114" s="56"/>
+      <c r="F114" s="58"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>1.8957345971563982E-6</v>
@@ -19168,13 +19221,13 @@
       <c r="B115" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C115" s="61"/>
-      <c r="D115" s="69"/>
-      <c r="E115" s="57">
+      <c r="C115" s="52"/>
+      <c r="D115" s="59"/>
+      <c r="E115" s="60">
         <f t="shared" si="13"/>
         <v>0.33175355450236965</v>
       </c>
-      <c r="F115" s="58"/>
+      <c r="F115" s="61"/>
       <c r="I115" s="18">
         <f t="shared" si="14"/>
         <v>3.3175355450236965E-7</v>
@@ -19190,7 +19243,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -19208,16 +19261,16 @@
       <c r="H120" s="24"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="48" t="s">
+      <c r="A121" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="48"/>
-      <c r="C121" s="48"/>
-      <c r="D121" s="48"/>
-      <c r="E121" s="48"/>
-      <c r="F121" s="48"/>
-      <c r="G121" s="48"/>
-      <c r="H121" s="48"/>
+      <c r="B121" s="70"/>
+      <c r="C121" s="70"/>
+      <c r="D121" s="70"/>
+      <c r="E121" s="70"/>
+      <c r="F121" s="70"/>
+      <c r="G121" s="70"/>
+      <c r="H121" s="70"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I122" s="16" t="s">
@@ -19261,14 +19314,14 @@
         <v>56</v>
       </c>
       <c r="B124" s="4"/>
-      <c r="C124" s="70">
+      <c r="C124" s="62">
         <v>2.5</v>
       </c>
-      <c r="D124" s="72"/>
-      <c r="E124" s="53">
+      <c r="D124" s="63"/>
+      <c r="E124" s="68">
         <v>0</v>
       </c>
-      <c r="F124" s="54"/>
+      <c r="F124" s="69"/>
       <c r="G124" s="35"/>
       <c r="I124" s="16">
         <f t="shared" ref="I124:I131" si="17">C124/1000000</f>
@@ -19288,10 +19341,10 @@
         <v>11</v>
       </c>
       <c r="B125" s="2"/>
-      <c r="C125" s="76">
+      <c r="C125" s="66">
         <v>5</v>
       </c>
-      <c r="D125" s="77"/>
+      <c r="D125" s="67"/>
       <c r="E125" s="50">
         <f>(B125+0.0053)/0.0019</f>
         <v>2.7894736842105265</v>
@@ -19318,10 +19371,10 @@
       <c r="B126" s="6">
         <v>2.3E-2</v>
       </c>
-      <c r="C126" s="59">
+      <c r="C126" s="48">
         <v>10</v>
       </c>
-      <c r="D126" s="75"/>
+      <c r="D126" s="49"/>
       <c r="E126" s="50">
         <f t="shared" ref="E126:E131" si="20">(B126+0.0053)/0.0019</f>
         <v>14.894736842105262</v>
@@ -19346,10 +19399,10 @@
         <v>12</v>
       </c>
       <c r="B127" s="6"/>
-      <c r="C127" s="59">
+      <c r="C127" s="48">
         <v>25</v>
       </c>
-      <c r="D127" s="75"/>
+      <c r="D127" s="49"/>
       <c r="E127" s="50">
         <f t="shared" si="20"/>
         <v>2.7894736842105265</v>
@@ -19376,10 +19429,10 @@
       <c r="B128" s="6">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C128" s="59">
+      <c r="C128" s="48">
         <v>50</v>
       </c>
-      <c r="D128" s="75"/>
+      <c r="D128" s="49"/>
       <c r="E128" s="50">
         <f t="shared" si="20"/>
         <v>53.315789473684212</v>
@@ -19406,10 +19459,10 @@
       <c r="B129" s="6">
         <v>0.20499999999999999</v>
       </c>
-      <c r="C129" s="59">
+      <c r="C129" s="48">
         <v>100</v>
       </c>
-      <c r="D129" s="75"/>
+      <c r="D129" s="49"/>
       <c r="E129" s="50">
         <f t="shared" si="20"/>
         <v>110.68421052631578</v>
@@ -19436,10 +19489,10 @@
       <c r="B130" s="6">
         <v>0.39500000000000002</v>
       </c>
-      <c r="C130" s="59">
+      <c r="C130" s="48">
         <v>200</v>
       </c>
-      <c r="D130" s="75"/>
+      <c r="D130" s="49"/>
       <c r="E130" s="50">
         <f t="shared" si="20"/>
         <v>210.68421052631581</v>
@@ -19466,15 +19519,15 @@
       <c r="B131" s="8">
         <v>0.97</v>
       </c>
-      <c r="C131" s="61">
+      <c r="C131" s="52">
         <v>500</v>
       </c>
-      <c r="D131" s="62"/>
-      <c r="E131" s="63">
+      <c r="D131" s="53"/>
+      <c r="E131" s="54">
         <f t="shared" si="20"/>
         <v>513.31578947368416</v>
       </c>
-      <c r="F131" s="64"/>
+      <c r="F131" s="55"/>
       <c r="G131" s="35"/>
       <c r="I131" s="19">
         <f t="shared" si="17"/>
@@ -19496,13 +19549,13 @@
       <c r="B132" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="C132" s="65"/>
+      <c r="C132" s="72"/>
       <c r="D132" s="78"/>
-      <c r="E132" s="81">
+      <c r="E132" s="79">
         <f t="shared" ref="E132" si="21">(B132+0.0053)/0.0019</f>
         <v>10.157894736842106</v>
       </c>
-      <c r="F132" s="82"/>
+      <c r="F132" s="80"/>
       <c r="G132" s="35"/>
       <c r="I132" s="18">
         <f>E132/1000000</f>
@@ -19524,8 +19577,8 @@
       <c r="B133" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="59"/>
-      <c r="D133" s="75"/>
+      <c r="C133" s="48"/>
+      <c r="D133" s="49"/>
       <c r="E133" s="50">
         <f t="shared" ref="E133" si="24">(B133+0.0053)/0.0019</f>
         <v>7.5263157894736841</v>
@@ -19552,8 +19605,8 @@
       <c r="B134" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C134" s="59"/>
-      <c r="D134" s="75"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
       <c r="E134" s="50">
         <f t="shared" ref="E134:E139" si="25">(B134+0.0053)/0.0019</f>
         <v>3.8421052631578947</v>
@@ -19580,8 +19633,8 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="59"/>
-      <c r="D135" s="75"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="50">
         <f t="shared" si="25"/>
         <v>2.7894736842105265</v>
@@ -19608,8 +19661,8 @@
       <c r="B136" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="75"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
       <c r="E136" s="50">
         <f t="shared" si="25"/>
         <v>5.9473684210526319</v>
@@ -19636,8 +19689,8 @@
       <c r="B137" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C137" s="59"/>
-      <c r="D137" s="75"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="50">
         <f t="shared" si="25"/>
         <v>15.947368421052632</v>
@@ -19664,8 +19717,8 @@
       <c r="B138" s="6">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="C138" s="59"/>
-      <c r="D138" s="75"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="49"/>
       <c r="E138" s="50">
         <f t="shared" si="25"/>
         <v>9.6315789473684212</v>
@@ -19692,13 +19745,13 @@
       <c r="B139" s="8">
         <v>1.4E-2</v>
       </c>
-      <c r="C139" s="61"/>
-      <c r="D139" s="62"/>
-      <c r="E139" s="63">
+      <c r="C139" s="52"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="54">
         <f t="shared" si="25"/>
         <v>10.157894736842106</v>
       </c>
-      <c r="F139" s="64"/>
+      <c r="F139" s="55"/>
       <c r="G139" s="35"/>
       <c r="I139" s="18">
         <f t="shared" si="26"/>
@@ -19715,32 +19768,55 @@
     </row>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="C126:D126"/>
     <mergeCell ref="E126:F126"/>
     <mergeCell ref="C113:D113"/>
@@ -19754,55 +19830,32 @@
     <mergeCell ref="E124:F124"/>
     <mergeCell ref="C125:D125"/>
     <mergeCell ref="E125:F125"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -19825,16 +19878,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="70" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -20049,14 +20102,14 @@
       <c r="B57" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C57" s="49">
+      <c r="C57" s="76">
         <v>1</v>
       </c>
-      <c r="D57" s="49"/>
-      <c r="E57" s="55">
+      <c r="D57" s="76"/>
+      <c r="E57" s="57">
         <v>0</v>
       </c>
-      <c r="F57" s="56"/>
+      <c r="F57" s="58"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -20068,15 +20121,15 @@
       <c r="B58" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="76">
         <v>2.5</v>
       </c>
-      <c r="D58" s="49"/>
-      <c r="E58" s="55">
+      <c r="D58" s="76"/>
+      <c r="E58" s="57">
         <f>(B58-0.0099)/0.0098</f>
         <v>0.82653061224489777</v>
       </c>
-      <c r="F58" s="56"/>
+      <c r="F58" s="58"/>
       <c r="H58" s="18"/>
       <c r="I58" s="27"/>
       <c r="J58" s="18"/>
@@ -20088,15 +20141,15 @@
       <c r="B59" s="6">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="76">
         <v>5</v>
       </c>
-      <c r="D59" s="49"/>
-      <c r="E59" s="55">
+      <c r="D59" s="76"/>
+      <c r="E59" s="57">
         <f t="shared" ref="E59:E64" si="0">(B59-0.0099)/0.0098</f>
         <v>3.3775510204081631</v>
       </c>
-      <c r="F59" s="56"/>
+      <c r="F59" s="58"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -20117,15 +20170,15 @@
       <c r="B60" s="6">
         <v>9.4E-2</v>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="76">
         <v>10</v>
       </c>
-      <c r="D60" s="49"/>
-      <c r="E60" s="55">
+      <c r="D60" s="76"/>
+      <c r="E60" s="57">
         <f t="shared" si="0"/>
         <v>8.5816326530612237</v>
       </c>
-      <c r="F60" s="56"/>
+      <c r="F60" s="58"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -20146,15 +20199,15 @@
       <c r="B61" s="6">
         <v>0.25</v>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="76">
         <v>25</v>
       </c>
-      <c r="D61" s="49"/>
-      <c r="E61" s="55">
+      <c r="D61" s="76"/>
+      <c r="E61" s="57">
         <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
-      <c r="F61" s="56"/>
+      <c r="F61" s="58"/>
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
       <c r="J61" s="21"/>
@@ -20166,15 +20219,15 @@
       <c r="B62" s="6">
         <v>0.52</v>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="76">
         <v>50</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="55">
+      <c r="D62" s="76"/>
+      <c r="E62" s="57">
         <f t="shared" si="0"/>
         <v>52.051020408163268</v>
       </c>
-      <c r="F62" s="56"/>
+      <c r="F62" s="58"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -20195,15 +20248,15 @@
       <c r="B63" s="6">
         <v>1.028</v>
       </c>
-      <c r="C63" s="49">
+      <c r="C63" s="76">
         <v>100</v>
       </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="55">
+      <c r="D63" s="76"/>
+      <c r="E63" s="57">
         <f t="shared" si="0"/>
         <v>103.88775510204081</v>
       </c>
-      <c r="F63" s="56"/>
+      <c r="F63" s="58"/>
       <c r="H63" s="18">
         <f>C63/1000000</f>
         <v>1E-4</v>
@@ -20224,15 +20277,15 @@
       <c r="B64" s="8">
         <v>1.95</v>
       </c>
-      <c r="C64" s="61">
+      <c r="C64" s="52">
         <v>200</v>
       </c>
-      <c r="D64" s="62"/>
-      <c r="E64" s="55">
+      <c r="D64" s="53"/>
+      <c r="E64" s="57">
         <f t="shared" si="0"/>
         <v>197.96938775510205</v>
       </c>
-      <c r="F64" s="56"/>
+      <c r="F64" s="58"/>
       <c r="H64" s="19">
         <f>C64/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -20253,13 +20306,13 @@
       <c r="B65" s="9">
         <v>0.224</v>
       </c>
-      <c r="C65" s="65"/>
-      <c r="D65" s="66"/>
-      <c r="E65" s="55">
+      <c r="C65" s="72"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="57">
         <f t="shared" ref="E65:E73" si="3">(B65-0.0099)/0.0098</f>
         <v>21.846938775510207</v>
       </c>
-      <c r="F65" s="56"/>
+      <c r="F65" s="58"/>
       <c r="H65" s="18">
         <f t="shared" ref="H65:H73" si="4">E65/1000000</f>
         <v>2.1846938775510207E-5</v>
@@ -20280,13 +20333,13 @@
       <c r="B66" s="6">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="C66" s="59"/>
-      <c r="D66" s="60"/>
-      <c r="E66" s="55">
+      <c r="C66" s="48"/>
+      <c r="D66" s="56"/>
+      <c r="E66" s="57">
         <f t="shared" si="3"/>
         <v>1.9489795918367347</v>
       </c>
-      <c r="F66" s="56"/>
+      <c r="F66" s="58"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>1.9489795918367348E-6</v>
@@ -20307,13 +20360,13 @@
       <c r="B67" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C67" s="59"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="55">
+      <c r="C67" s="48"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="57">
         <f t="shared" si="3"/>
         <v>1.4387755102040816</v>
       </c>
-      <c r="F67" s="56"/>
+      <c r="F67" s="58"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>1.4387755102040816E-6</v>
@@ -20334,13 +20387,13 @@
       <c r="B68" s="6">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="C68" s="59"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="55">
+      <c r="C68" s="48"/>
+      <c r="D68" s="56"/>
+      <c r="E68" s="57">
         <f t="shared" si="3"/>
         <v>7.0510204081632653</v>
       </c>
-      <c r="F68" s="56"/>
+      <c r="F68" s="58"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>7.051020408163265E-6</v>
@@ -20361,13 +20414,13 @@
       <c r="B69" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="55">
+      <c r="C69" s="48"/>
+      <c r="D69" s="56"/>
+      <c r="E69" s="57">
         <f t="shared" si="3"/>
         <v>3.1734693877551026</v>
       </c>
-      <c r="F69" s="56"/>
+      <c r="F69" s="58"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>3.1734693877551026E-6</v>
@@ -20388,13 +20441,13 @@
       <c r="B70" s="6">
         <v>0.224</v>
       </c>
-      <c r="C70" s="59"/>
-      <c r="D70" s="60"/>
-      <c r="E70" s="55">
+      <c r="C70" s="48"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="57">
         <f t="shared" si="3"/>
         <v>21.846938775510207</v>
       </c>
-      <c r="F70" s="56"/>
+      <c r="F70" s="58"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>2.1846938775510207E-5</v>
@@ -20415,13 +20468,13 @@
       <c r="B71" s="6">
         <v>0.221</v>
       </c>
-      <c r="C71" s="59"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="55">
+      <c r="C71" s="48"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="57">
         <f t="shared" si="3"/>
         <v>21.540816326530614</v>
       </c>
-      <c r="F71" s="56"/>
+      <c r="F71" s="58"/>
       <c r="H71" s="18">
         <f t="shared" si="4"/>
         <v>2.1540816326530614E-5</v>
@@ -20442,13 +20495,13 @@
       <c r="B72" s="6">
         <v>0.11700000000000001</v>
       </c>
-      <c r="C72" s="59"/>
-      <c r="D72" s="60"/>
-      <c r="E72" s="55">
+      <c r="C72" s="48"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="57">
         <f t="shared" si="3"/>
         <v>10.928571428571429</v>
       </c>
-      <c r="F72" s="56"/>
+      <c r="F72" s="58"/>
       <c r="H72" s="18">
         <f t="shared" si="4"/>
         <v>1.0928571428571429E-5</v>
@@ -20469,13 +20522,13 @@
       <c r="B73" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C73" s="59"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="55">
+      <c r="C73" s="48"/>
+      <c r="D73" s="56"/>
+      <c r="E73" s="57">
         <f t="shared" si="3"/>
         <v>2.5612244897959191</v>
       </c>
-      <c r="F73" s="56"/>
+      <c r="F73" s="58"/>
       <c r="H73" s="18">
         <f t="shared" si="4"/>
         <v>2.5612244897959191E-6</v>
@@ -20560,11 +20613,11 @@
         <v>0.5</v>
       </c>
       <c r="D103" s="11"/>
-      <c r="E103" s="53">
+      <c r="E103" s="68">
         <f>(B103+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F103" s="54"/>
+      <c r="F103" s="69"/>
       <c r="I103" s="16">
         <f t="shared" ref="I103:I108" si="7">C103/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -20589,11 +20642,11 @@
         <v>1</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="55">
+      <c r="E104" s="57">
         <f t="shared" ref="E104:E108" si="9">(B104+0.001)/0.0201</f>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F104" s="56"/>
+      <c r="F104" s="58"/>
       <c r="I104" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999995E-7</v>
@@ -20618,11 +20671,11 @@
         <v>5</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="55">
+      <c r="E105" s="57">
         <f t="shared" si="9"/>
         <v>4.1293532338308463</v>
       </c>
-      <c r="F105" s="56"/>
+      <c r="F105" s="58"/>
       <c r="I105" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000004E-6</v>
@@ -20647,11 +20700,11 @@
         <v>10</v>
       </c>
       <c r="D106" s="13"/>
-      <c r="E106" s="55">
+      <c r="E106" s="57">
         <f t="shared" si="9"/>
         <v>10.149253731343284</v>
       </c>
-      <c r="F106" s="56"/>
+      <c r="F106" s="58"/>
       <c r="I106" s="18">
         <f t="shared" si="7"/>
         <v>1.0000000000000001E-5</v>
@@ -20676,11 +20729,11 @@
         <v>25</v>
       </c>
       <c r="D107" s="33"/>
-      <c r="E107" s="55">
+      <c r="E107" s="57">
         <f t="shared" si="9"/>
         <v>24.427860696517413</v>
       </c>
-      <c r="F107" s="56"/>
+      <c r="F107" s="58"/>
       <c r="I107" s="19">
         <f t="shared" si="7"/>
         <v>2.5000000000000001E-5</v>
@@ -20703,11 +20756,11 @@
         <v>50</v>
       </c>
       <c r="D108" s="15"/>
-      <c r="E108" s="57">
+      <c r="E108" s="60">
         <f t="shared" si="9"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F108" s="58"/>
+      <c r="F108" s="61"/>
       <c r="I108" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000002E-5</v>
@@ -20728,13 +20781,13 @@
       <c r="B109" s="9">
         <v>0</v>
       </c>
-      <c r="C109" s="65"/>
-      <c r="D109" s="66"/>
-      <c r="E109" s="67">
+      <c r="C109" s="72"/>
+      <c r="D109" s="73"/>
+      <c r="E109" s="74">
         <f t="shared" ref="E109" si="11">(B109+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F109" s="68"/>
+      <c r="F109" s="75"/>
       <c r="I109" s="18">
         <f>E109/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -20755,13 +20808,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="59"/>
-      <c r="D110" s="60"/>
-      <c r="E110" s="55">
+      <c r="C110" s="48"/>
+      <c r="D110" s="56"/>
+      <c r="E110" s="57">
         <f t="shared" ref="E110:E117" si="12">(B110+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F110" s="56"/>
+      <c r="F110" s="58"/>
       <c r="I110" s="18">
         <f t="shared" ref="I110:I117" si="13">E110/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -20782,13 +20835,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="59"/>
-      <c r="D111" s="60"/>
-      <c r="E111" s="55">
+      <c r="C111" s="48"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F111" s="56"/>
+      <c r="F111" s="58"/>
       <c r="I111" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20809,13 +20862,13 @@
       <c r="B112" s="6">
         <v>0</v>
       </c>
-      <c r="C112" s="59"/>
-      <c r="D112" s="60"/>
-      <c r="E112" s="55">
+      <c r="C112" s="48"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F112" s="56"/>
+      <c r="F112" s="58"/>
       <c r="I112" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20836,13 +20889,13 @@
       <c r="B113" s="6">
         <v>0</v>
       </c>
-      <c r="C113" s="59"/>
-      <c r="D113" s="60"/>
-      <c r="E113" s="55">
+      <c r="C113" s="48"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F113" s="56"/>
+      <c r="F113" s="58"/>
       <c r="I113" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20863,13 +20916,13 @@
       <c r="B114" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C114" s="59"/>
-      <c r="D114" s="60"/>
-      <c r="E114" s="55">
+      <c r="C114" s="48"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="57">
         <f t="shared" si="12"/>
         <v>0.1492537313432836</v>
       </c>
-      <c r="F114" s="56"/>
+      <c r="F114" s="58"/>
       <c r="I114" s="18">
         <f t="shared" si="13"/>
         <v>1.492537313432836E-7</v>
@@ -20890,13 +20943,13 @@
       <c r="B115" s="6">
         <v>0.01</v>
       </c>
-      <c r="C115" s="59"/>
-      <c r="D115" s="60"/>
-      <c r="E115" s="55">
+      <c r="C115" s="48"/>
+      <c r="D115" s="56"/>
+      <c r="E115" s="57">
         <f t="shared" si="12"/>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F115" s="56"/>
+      <c r="F115" s="58"/>
       <c r="I115" s="18">
         <f t="shared" si="13"/>
         <v>5.4726368159203972E-7</v>
@@ -20917,13 +20970,13 @@
       <c r="B116" s="6">
         <v>0</v>
       </c>
-      <c r="C116" s="59"/>
-      <c r="D116" s="60"/>
-      <c r="E116" s="55">
+      <c r="C116" s="48"/>
+      <c r="D116" s="56"/>
+      <c r="E116" s="57">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F116" s="56"/>
+      <c r="F116" s="58"/>
       <c r="I116" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20944,13 +20997,13 @@
       <c r="B117" s="8">
         <v>0</v>
       </c>
-      <c r="C117" s="61"/>
-      <c r="D117" s="69"/>
-      <c r="E117" s="57">
+      <c r="C117" s="52"/>
+      <c r="D117" s="59"/>
+      <c r="E117" s="60">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F117" s="58"/>
+      <c r="F117" s="61"/>
       <c r="I117" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20966,7 +21019,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I120" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
       <c r="K120">
         <v>62.005400000000002</v>
@@ -20982,16 +21035,16 @@
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="48" t="s">
+      <c r="A122" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B122" s="48"/>
-      <c r="C122" s="48"/>
-      <c r="D122" s="48"/>
-      <c r="E122" s="48"/>
-      <c r="F122" s="48"/>
-      <c r="G122" s="48"/>
-      <c r="H122" s="48"/>
+      <c r="B122" s="70"/>
+      <c r="C122" s="70"/>
+      <c r="D122" s="70"/>
+      <c r="E122" s="70"/>
+      <c r="F122" s="70"/>
+      <c r="G122" s="70"/>
+      <c r="H122" s="70"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I123" s="16" t="s">
@@ -21035,14 +21088,14 @@
         <v>56</v>
       </c>
       <c r="B125" s="4"/>
-      <c r="C125" s="70">
+      <c r="C125" s="62">
         <v>2.5</v>
       </c>
-      <c r="D125" s="72"/>
-      <c r="E125" s="53">
+      <c r="D125" s="63"/>
+      <c r="E125" s="68">
         <v>0</v>
       </c>
-      <c r="F125" s="54"/>
+      <c r="F125" s="69"/>
       <c r="G125" s="35"/>
       <c r="I125" s="16">
         <f t="shared" ref="I125:I132" si="16">C125/1000000</f>
@@ -21062,10 +21115,10 @@
         <v>11</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="76">
+      <c r="C126" s="66">
         <v>5</v>
       </c>
-      <c r="D126" s="77"/>
+      <c r="D126" s="67"/>
       <c r="E126" s="50">
         <f>(B126-0.0011)/0.0019</f>
         <v>-0.57894736842105265</v>
@@ -21092,10 +21145,10 @@
       <c r="B127" s="6">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C127" s="59">
+      <c r="C127" s="48">
         <v>10</v>
       </c>
-      <c r="D127" s="75"/>
+      <c r="D127" s="49"/>
       <c r="E127" s="50">
         <f t="shared" ref="E127:E141" si="18">(B127-0.0011)/0.0019</f>
         <v>11</v>
@@ -21120,10 +21173,10 @@
         <v>12</v>
       </c>
       <c r="B128" s="6"/>
-      <c r="C128" s="59">
+      <c r="C128" s="48">
         <v>25</v>
       </c>
-      <c r="D128" s="75"/>
+      <c r="D128" s="49"/>
       <c r="E128" s="50">
         <f t="shared" si="18"/>
         <v>-0.57894736842105265</v>
@@ -21150,10 +21203,10 @@
       <c r="B129" s="6">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C129" s="59">
+      <c r="C129" s="48">
         <v>50</v>
       </c>
-      <c r="D129" s="75"/>
+      <c r="D129" s="49"/>
       <c r="E129" s="50">
         <f t="shared" si="18"/>
         <v>53.105263157894733</v>
@@ -21180,10 +21233,10 @@
       <c r="B130" s="6">
         <v>0.19400000000000001</v>
       </c>
-      <c r="C130" s="59">
+      <c r="C130" s="48">
         <v>100</v>
       </c>
-      <c r="D130" s="75"/>
+      <c r="D130" s="49"/>
       <c r="E130" s="50">
         <f t="shared" si="18"/>
         <v>101.5263157894737</v>
@@ -21210,10 +21263,10 @@
       <c r="B131" s="6">
         <v>0.376</v>
       </c>
-      <c r="C131" s="59">
+      <c r="C131" s="48">
         <v>200</v>
       </c>
-      <c r="D131" s="75"/>
+      <c r="D131" s="49"/>
       <c r="E131" s="50">
         <f t="shared" si="18"/>
         <v>197.31578947368422</v>
@@ -21240,15 +21293,15 @@
       <c r="B132" s="8">
         <v>0.96699999999999997</v>
       </c>
-      <c r="C132" s="61">
+      <c r="C132" s="52">
         <v>500</v>
       </c>
-      <c r="D132" s="62"/>
-      <c r="E132" s="63">
+      <c r="D132" s="53"/>
+      <c r="E132" s="54">
         <f t="shared" si="18"/>
         <v>508.36842105263156</v>
       </c>
-      <c r="F132" s="64"/>
+      <c r="F132" s="55"/>
       <c r="G132" s="35"/>
       <c r="I132" s="19">
         <f t="shared" si="16"/>
@@ -21270,13 +21323,13 @@
       <c r="B133" s="9">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="65"/>
+      <c r="C133" s="72"/>
       <c r="D133" s="78"/>
-      <c r="E133" s="81">
+      <c r="E133" s="79">
         <f t="shared" si="18"/>
         <v>4.1578947368421044</v>
       </c>
-      <c r="F133" s="82"/>
+      <c r="F133" s="80"/>
       <c r="G133" s="35"/>
       <c r="I133" s="18">
         <f>E133/1000000</f>
@@ -21298,8 +21351,8 @@
       <c r="B134" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C134" s="59"/>
-      <c r="D134" s="75"/>
+      <c r="C134" s="48"/>
+      <c r="D134" s="49"/>
       <c r="E134" s="50">
         <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
@@ -21326,8 +21379,8 @@
       <c r="B135" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C135" s="59"/>
-      <c r="D135" s="75"/>
+      <c r="C135" s="48"/>
+      <c r="D135" s="49"/>
       <c r="E135" s="50">
         <f t="shared" si="18"/>
         <v>5.2105263157894735</v>
@@ -21354,8 +21407,8 @@
       <c r="B136" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="75"/>
+      <c r="C136" s="48"/>
+      <c r="D136" s="49"/>
       <c r="E136" s="50">
         <f t="shared" si="18"/>
         <v>3.1052631578947367</v>
@@ -21382,8 +21435,8 @@
       <c r="B137" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C137" s="59"/>
-      <c r="D137" s="75"/>
+      <c r="C137" s="48"/>
+      <c r="D137" s="49"/>
       <c r="E137" s="50">
         <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
@@ -21410,8 +21463,8 @@
       <c r="B138" s="6">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C138" s="59"/>
-      <c r="D138" s="75"/>
+      <c r="C138" s="48"/>
+      <c r="D138" s="49"/>
       <c r="E138" s="50">
         <f t="shared" si="18"/>
         <v>23.105263157894736</v>
@@ -21438,8 +21491,8 @@
       <c r="B139" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C139" s="59"/>
-      <c r="D139" s="75"/>
+      <c r="C139" s="48"/>
+      <c r="D139" s="49"/>
       <c r="E139" s="50">
         <f t="shared" si="18"/>
         <v>18.368421052631579</v>
@@ -21466,8 +21519,8 @@
       <c r="B140" s="6">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C140" s="59"/>
-      <c r="D140" s="75"/>
+      <c r="C140" s="48"/>
+      <c r="D140" s="49"/>
       <c r="E140" s="50">
         <f t="shared" si="18"/>
         <v>13.105263157894736</v>
@@ -21494,13 +21547,13 @@
       <c r="B141" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C141" s="61"/>
-      <c r="D141" s="62"/>
-      <c r="E141" s="63">
+      <c r="C141" s="52"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="54">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="F141" s="64"/>
+      <c r="F141" s="55"/>
       <c r="I141" s="18">
         <f t="shared" si="22"/>
         <v>9.9999999999999995E-7</v>
@@ -21516,6 +21569,84 @@
     </row>
   </sheetData>
   <mergeCells count="94">
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="E137:F137"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="E136:F136"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="E73:F73"/>
@@ -21532,84 +21663,6 @@
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:F63"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C136:D136"/>
-    <mergeCell ref="E136:F136"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="C137:D137"/>
-    <mergeCell ref="E137:F137"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="C139:D139"/>
-    <mergeCell ref="E139:F139"/>
   </mergeCells>
   <pageMargins left="0.11458333333333333" right="1.0416666666666666E-2" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -22516,220 +22569,401 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB11AC0-5135-4DD2-A5FB-6D266A3E4B2C}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="43" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="84">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="87" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="89" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="90" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="90" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="95">
+        <v>1</v>
+      </c>
+      <c r="B4" s="83">
+        <v>0.40045619999999998</v>
+      </c>
+      <c r="C4" s="83">
+        <v>0.80183163800000001</v>
+      </c>
+      <c r="D4" s="83">
+        <v>7.1953829999999996E-3</v>
+      </c>
+      <c r="E4" s="83">
+        <v>7.0582400000000003E-3</v>
+      </c>
+      <c r="F4" s="83">
+        <v>0.32144899999999998</v>
+      </c>
+      <c r="G4" s="84">
+        <v>0.25785028199999999</v>
+      </c>
+      <c r="H4" s="85"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="95">
+        <v>2</v>
+      </c>
+      <c r="B5" s="83">
+        <v>2.01386E-2</v>
+      </c>
+      <c r="C5" s="83">
+        <v>3.6000381999999997E-2</v>
+      </c>
+      <c r="D5" s="83">
+        <v>2.604468E-3</v>
+      </c>
+      <c r="E5" s="83">
+        <v>1.8052179999999999E-3</v>
+      </c>
+      <c r="F5" s="83">
+        <v>0.12944990000000001</v>
+      </c>
+      <c r="G5" s="84">
+        <v>0.15678319700000001</v>
+      </c>
+      <c r="H5" s="85"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="94">
+        <v>3</v>
+      </c>
+      <c r="B6" s="91">
         <v>0.51456029999999997</v>
       </c>
-      <c r="C4" s="84">
+      <c r="C6" s="91">
+        <v>0.59243359299999998</v>
+      </c>
+      <c r="D6" s="91">
         <v>1.4198677E-2</v>
       </c>
-      <c r="D4" s="84">
+      <c r="E6" s="91">
+        <v>1.3739723000000001E-2</v>
+      </c>
+      <c r="F6" s="91">
         <v>0.90296929999999997</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" s="84">
-        <v>2.01386E-2</v>
-      </c>
-      <c r="C5" s="84">
-        <v>2.604468E-3</v>
-      </c>
-      <c r="D5" s="84">
-        <v>0.12944990000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="84">
-        <v>0.40045619999999998</v>
-      </c>
-      <c r="C6" s="84">
-        <v>7.1953829999999996E-3</v>
-      </c>
-      <c r="D6" s="84">
-        <v>0.32144899999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G6" s="92">
+        <v>0.34503958499999998</v>
+      </c>
+      <c r="H6" s="85"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="85"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="87" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="83" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="83" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="B11" s="93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" s="90" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="90" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="90" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="88" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="83">
+        <v>0.11294683</v>
+      </c>
+      <c r="C12" s="83">
+        <v>7.7492951000000004E-2</v>
+      </c>
+      <c r="D12" s="83">
+        <v>1.17862977E-2</v>
+      </c>
+      <c r="E12" s="83">
+        <v>7.4871069999999998E-3</v>
+      </c>
+      <c r="F12" s="83">
+        <v>0.13216940999999999</v>
+      </c>
+      <c r="G12" s="84">
+        <v>0.174820211</v>
+      </c>
+      <c r="H12" s="85"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="88" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" s="83">
+        <v>0.68796553999999999</v>
+      </c>
+      <c r="C13" s="83">
+        <v>1.12860228</v>
+      </c>
+      <c r="D13" s="83">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E13" s="83">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F13" s="83">
+        <v>0.51072868999999999</v>
+      </c>
+      <c r="G13" s="84">
+        <v>0.170398352</v>
+      </c>
+      <c r="H13" s="85"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="88" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="83">
+        <v>3.7810209999999997E-2</v>
+      </c>
+      <c r="C14" s="83">
+        <v>6.0655305999999999E-2</v>
+      </c>
+      <c r="D14" s="83">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E14" s="83">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F14" s="83">
+        <v>9.1376379999999993E-2</v>
+      </c>
+      <c r="G14" s="84">
+        <v>0.10581473</v>
+      </c>
+      <c r="H14" s="85"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="83">
+        <v>1.151371E-2</v>
+      </c>
+      <c r="C15" s="83">
+        <v>1.6578053999999998E-2</v>
+      </c>
+      <c r="D15" s="83">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E15" s="83">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F15" s="83">
+        <v>0.15664522</v>
+      </c>
+      <c r="G15" s="84">
+        <v>0.22000215300000001</v>
+      </c>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="88" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="83">
+        <v>1.109189E-2</v>
+      </c>
+      <c r="C16" s="83">
+        <v>1.3172427E-2</v>
+      </c>
+      <c r="D16" s="83">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E16" s="83">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F16" s="83">
+        <v>0.14032801</v>
+      </c>
+      <c r="G16" s="84">
+        <v>0.16569803899999999</v>
+      </c>
+      <c r="H16" s="85"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="84">
+      <c r="B17" s="83">
         <v>0.22730737000000001</v>
       </c>
-      <c r="C12" s="84">
+      <c r="C17" s="83">
+        <v>0.25255018699999998</v>
+      </c>
+      <c r="D17" s="83">
         <v>6.5395380999999997E-3</v>
       </c>
-      <c r="D12" s="84">
+      <c r="E17" s="83">
+        <v>4.1370260000000002E-3</v>
+      </c>
+      <c r="F17" s="83">
         <v>0.91050034999999996</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="G17" s="84">
+        <v>0.23094473900000001</v>
+      </c>
+      <c r="H17" s="85"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="B13" s="84">
+      <c r="B18" s="83">
         <v>0.98818676999999999</v>
       </c>
-      <c r="C13" s="84">
+      <c r="C18" s="83">
+        <v>0.87578789000000001</v>
+      </c>
+      <c r="D18" s="83">
         <v>3.0426010900000001E-2</v>
       </c>
-      <c r="D13" s="84">
+      <c r="E18" s="83">
+        <v>1.3874948E-2</v>
+      </c>
+      <c r="F18" s="83">
         <v>1.00024501</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="G18" s="84">
+        <v>0.26870768299999997</v>
+      </c>
+      <c r="H18" s="85"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="84">
+      <c r="B19" s="83">
         <v>0.44527673000000001</v>
       </c>
-      <c r="C14" s="84">
+      <c r="C19" s="83">
+        <v>0.29066925799999999</v>
+      </c>
+      <c r="D19" s="83">
         <v>8.9557908999999998E-3</v>
       </c>
-      <c r="D14" s="84">
+      <c r="E19" s="83">
+        <v>4.5329439999999997E-3</v>
+      </c>
+      <c r="F19" s="83">
         <v>1.00840361</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="G19" s="84">
+        <v>0.29566137100000001</v>
+      </c>
+      <c r="H19" s="85"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="84">
+      <c r="B20" s="91">
         <v>4.620055E-2</v>
       </c>
-      <c r="C15" s="84">
+      <c r="C20" s="91" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="91">
         <v>8.9743579999999998E-4</v>
       </c>
-      <c r="D15" s="84">
+      <c r="E20" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="92">
         <v>6.2005400000000002E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="84">
-        <v>3.7810209999999997E-2</v>
-      </c>
-      <c r="C16" s="84">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="D16" s="84">
-        <v>9.1376379999999993E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="84">
-        <v>1.151371E-2</v>
-      </c>
-      <c r="C17" s="84">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="D17" s="84">
-        <v>0.15664522</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B18" s="84">
-        <v>1.109189E-2</v>
-      </c>
-      <c r="C18" s="84">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="D18" s="84">
-        <v>0.14032801</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="84">
-        <v>0.11294683</v>
-      </c>
-      <c r="C19" s="84">
-        <v>1.17862977E-2</v>
-      </c>
-      <c r="D19" s="84">
-        <v>0.13216940999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="84">
-        <v>0.68796553999999999</v>
-      </c>
-      <c r="C20" s="84">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="D20" s="84">
-        <v>0.51072868999999999</v>
-      </c>
+      <c r="G20" s="92" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="85"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Wasser/Photometrische Messung (Stefan)/3 Auswertung Photometrie.xlsx
+++ b/Wasser/Photometrische Messung (Stefan)/3 Auswertung Photometrie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexandra\Documents\GitHub\Moore-Lichtenau-Meusebach\Wasser\Photometrische Messung (Stefan)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7199CADE-C578-420E-9594-CCACFC2B4822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A0DF2E-438C-47A2-9D18-1C4E444BDF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.06.2025" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Zusammenfassung" sheetId="7" r:id="rId5"/>
     <sheet name="Ergebnisse" sheetId="8" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Zusammenfassung!$A$1:$G$37</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="135">
   <si>
     <t>sample</t>
   </si>
@@ -415,15 +418,6 @@
     <t>Messstelle</t>
   </si>
   <si>
-    <t xml:space="preserve">Mittelwerte je Fläche </t>
-  </si>
-  <si>
-    <t>Mittelwerte je Logger</t>
-  </si>
-  <si>
-    <t>Fläche</t>
-  </si>
-  <si>
     <t>Molgewicht  NO3</t>
   </si>
   <si>
@@ -444,6 +438,18 @@
   <si>
     <t>NO₃⁻ [mg/L]</t>
   </si>
+  <si>
+    <t>Fläche 1</t>
+  </si>
+  <si>
+    <t>Fläche 2</t>
+  </si>
+  <si>
+    <t>Fläche 3</t>
+  </si>
+  <si>
+    <t>Flächen-Mittelwert</t>
+  </si>
 </sst>
 </file>
 
@@ -451,7 +457,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
@@ -1608,6 +1614,38 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1713,37 +1751,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -14748,16 +14756,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -14963,14 +14971,14 @@
       <c r="B55" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C55" s="77">
+      <c r="C55" s="89">
         <v>1</v>
       </c>
-      <c r="D55" s="77"/>
-      <c r="E55" s="68">
+      <c r="D55" s="89"/>
+      <c r="E55" s="80">
         <v>0</v>
       </c>
-      <c r="F55" s="69"/>
+      <c r="F55" s="81"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -14982,15 +14990,15 @@
       <c r="B56" s="6">
         <v>1.6E-2</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="88">
         <v>2.5</v>
       </c>
-      <c r="D56" s="76"/>
-      <c r="E56" s="57">
+      <c r="D56" s="88"/>
+      <c r="E56" s="69">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-4.3010752688172157E-2</v>
       </c>
-      <c r="F56" s="58"/>
+      <c r="F56" s="70"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -15002,15 +15010,15 @@
       <c r="B57" s="6">
         <v>0.04</v>
       </c>
-      <c r="C57" s="76">
+      <c r="C57" s="88">
         <v>5</v>
       </c>
-      <c r="D57" s="76"/>
-      <c r="E57" s="57">
+      <c r="D57" s="88"/>
+      <c r="E57" s="69">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.5376344086021505</v>
       </c>
-      <c r="F57" s="58"/>
+      <c r="F57" s="70"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -15031,15 +15039,15 @@
       <c r="B58" s="6">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="C58" s="76">
+      <c r="C58" s="88">
         <v>10</v>
       </c>
-      <c r="D58" s="76"/>
-      <c r="E58" s="50">
+      <c r="D58" s="88"/>
+      <c r="E58" s="62">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.2688172043010768</v>
       </c>
-      <c r="F58" s="51"/>
+      <c r="F58" s="63"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -15060,15 +15068,15 @@
       <c r="B59" s="6">
         <v>0.22800000000000001</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="88">
         <v>25</v>
       </c>
-      <c r="D59" s="76"/>
-      <c r="E59" s="50">
+      <c r="D59" s="88"/>
+      <c r="E59" s="62">
         <f t="shared" si="1"/>
         <v>22.752688172043015</v>
       </c>
-      <c r="F59" s="51"/>
+      <c r="F59" s="63"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -15080,15 +15088,15 @@
       <c r="B60" s="6">
         <v>0.54300000000000004</v>
       </c>
-      <c r="C60" s="76">
+      <c r="C60" s="88">
         <v>50</v>
       </c>
-      <c r="D60" s="76"/>
-      <c r="E60" s="50">
+      <c r="D60" s="88"/>
+      <c r="E60" s="62">
         <f t="shared" si="1"/>
         <v>56.62365591397851</v>
       </c>
-      <c r="F60" s="51"/>
+      <c r="F60" s="63"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -15109,15 +15117,15 @@
       <c r="B61" s="6">
         <v>0.98199999999999998</v>
       </c>
-      <c r="C61" s="76">
+      <c r="C61" s="88">
         <v>100</v>
       </c>
-      <c r="D61" s="76"/>
-      <c r="E61" s="50">
+      <c r="D61" s="88"/>
+      <c r="E61" s="62">
         <f t="shared" si="1"/>
         <v>103.82795698924733</v>
       </c>
-      <c r="F61" s="51"/>
+      <c r="F61" s="63"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -15138,15 +15146,15 @@
       <c r="B62" s="8">
         <v>1.8460000000000001</v>
       </c>
-      <c r="C62" s="52">
+      <c r="C62" s="64">
         <v>200</v>
       </c>
-      <c r="D62" s="53"/>
-      <c r="E62" s="54">
+      <c r="D62" s="65"/>
+      <c r="E62" s="66">
         <f t="shared" si="1"/>
         <v>196.73118279569894</v>
       </c>
-      <c r="F62" s="55"/>
+      <c r="F62" s="67"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -15167,12 +15175,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="73"/>
-      <c r="E63" s="74">
+      <c r="C63" s="84"/>
+      <c r="D63" s="85"/>
+      <c r="E63" s="86">
         <v>0</v>
       </c>
-      <c r="F63" s="75"/>
+      <c r="F63" s="87"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -15193,12 +15201,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="48"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="57">
+      <c r="C64" s="60"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="69">
         <v>0</v>
       </c>
-      <c r="F64" s="58"/>
+      <c r="F64" s="70"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15219,12 +15227,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="57">
+      <c r="C65" s="60"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="69">
         <v>0</v>
       </c>
-      <c r="F65" s="58"/>
+      <c r="F65" s="70"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15245,12 +15253,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="48"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="57">
+      <c r="C66" s="60"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="69">
         <v>0</v>
       </c>
-      <c r="F66" s="58"/>
+      <c r="F66" s="70"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -15271,13 +15279,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="57">
+      <c r="C67" s="60"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="69">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="58"/>
+      <c r="F67" s="70"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -15298,13 +15306,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="57">
+      <c r="C68" s="60"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="69">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="58"/>
+      <c r="F68" s="70"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -15325,13 +15333,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="57">
+      <c r="C69" s="60"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="69">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="58"/>
+      <c r="F69" s="70"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -15352,13 +15360,13 @@
       <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="52"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="60">
+      <c r="C70" s="64"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="72">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="61"/>
+      <c r="F70" s="73"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -15443,11 +15451,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="68">
+      <c r="E101" s="80">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="69"/>
+      <c r="F101" s="81"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -15472,11 +15480,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="57">
+      <c r="E102" s="69">
         <f t="shared" ref="E102:E106" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="58"/>
+      <c r="F102" s="70"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -15501,11 +15509,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="57">
+      <c r="E103" s="69">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="58"/>
+      <c r="F103" s="70"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -15530,11 +15538,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="57">
+      <c r="E104" s="69">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="58"/>
+      <c r="F104" s="70"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -15559,11 +15567,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="57">
+      <c r="E105" s="69">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="58"/>
+      <c r="F105" s="70"/>
       <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -15588,11 +15596,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="60">
+      <c r="E106" s="72">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="61"/>
+      <c r="F106" s="73"/>
       <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -15613,13 +15621,13 @@
       <c r="B107" s="4">
         <v>0</v>
       </c>
-      <c r="C107" s="62"/>
-      <c r="D107" s="71"/>
-      <c r="E107" s="68">
+      <c r="C107" s="74"/>
+      <c r="D107" s="83"/>
+      <c r="E107" s="80">
         <f t="shared" ref="E107" si="12">(B107+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="69"/>
+      <c r="F107" s="81"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15640,13 +15648,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="48"/>
-      <c r="D108" s="56"/>
-      <c r="E108" s="57">
+      <c r="C108" s="60"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="69">
         <f t="shared" ref="E108:E114" si="13">(B108+0.0049)/0.0204</f>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="58"/>
+      <c r="F108" s="70"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="14">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -15667,13 +15675,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="48"/>
-      <c r="D109" s="56"/>
-      <c r="E109" s="57">
+      <c r="C109" s="60"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="69">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="58"/>
+      <c r="F109" s="70"/>
       <c r="I109" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15694,13 +15702,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="48"/>
-      <c r="D110" s="56"/>
-      <c r="E110" s="57">
+      <c r="C110" s="60"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="69">
         <f t="shared" si="13"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="58"/>
+      <c r="F110" s="70"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>2.4019607843137255E-7</v>
@@ -15721,13 +15729,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="57">
+      <c r="C111" s="60"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="69">
         <f t="shared" si="13"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="58"/>
+      <c r="F111" s="70"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>9.2647058823529408E-7</v>
@@ -15748,13 +15756,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="48"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="57">
+      <c r="C112" s="60"/>
+      <c r="D112" s="68"/>
+      <c r="E112" s="69">
         <f t="shared" si="13"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="58"/>
+      <c r="F112" s="70"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>6.8137254901960776E-7</v>
@@ -15775,13 +15783,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="48"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="57">
+      <c r="C113" s="60"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69">
         <f t="shared" si="13"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="58"/>
+      <c r="F113" s="70"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>2.1519607843137253E-6</v>
@@ -15802,13 +15810,13 @@
       <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="52"/>
-      <c r="D114" s="59"/>
-      <c r="E114" s="60">
+      <c r="C114" s="64"/>
+      <c r="D114" s="71"/>
+      <c r="E114" s="72">
         <f t="shared" si="13"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="61"/>
+      <c r="F114" s="73"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>5.3431372549019611E-7</v>
@@ -15824,7 +15832,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -15840,16 +15848,16 @@
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="70" t="s">
+      <c r="A120" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="70"/>
-      <c r="C120" s="70"/>
-      <c r="D120" s="70"/>
-      <c r="E120" s="70"/>
-      <c r="F120" s="70"/>
-      <c r="G120" s="70"/>
-      <c r="H120" s="70"/>
+      <c r="B120" s="82"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="82"/>
+      <c r="E120" s="82"/>
+      <c r="F120" s="82"/>
+      <c r="G120" s="82"/>
+      <c r="H120" s="82"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I121" s="16" t="s">
@@ -15895,14 +15903,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="62">
+      <c r="C123" s="74">
         <v>2.5</v>
       </c>
-      <c r="D123" s="63"/>
-      <c r="E123" s="68">
+      <c r="D123" s="75"/>
+      <c r="E123" s="80">
         <v>0</v>
       </c>
-      <c r="F123" s="69"/>
+      <c r="F123" s="81"/>
       <c r="G123" s="35"/>
       <c r="I123" s="16">
         <f t="shared" ref="I123:I130" si="17">C123/1000000</f>
@@ -15924,15 +15932,15 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="66">
+      <c r="C124" s="78">
         <v>5</v>
       </c>
-      <c r="D124" s="67"/>
-      <c r="E124" s="50">
+      <c r="D124" s="79"/>
+      <c r="E124" s="62">
         <f t="shared" ref="E124:E130" si="18">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="51"/>
+      <c r="F124" s="63"/>
       <c r="G124" s="35"/>
       <c r="I124" s="18">
         <f t="shared" si="17"/>
@@ -15954,15 +15962,15 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="48">
+      <c r="C125" s="60">
         <v>10</v>
       </c>
-      <c r="D125" s="49"/>
-      <c r="E125" s="50">
+      <c r="D125" s="61"/>
+      <c r="E125" s="62">
         <f t="shared" si="18"/>
         <v>7.7368421052631584</v>
       </c>
-      <c r="F125" s="51"/>
+      <c r="F125" s="63"/>
       <c r="G125" s="35"/>
       <c r="I125" s="18">
         <f t="shared" si="17"/>
@@ -15984,15 +15992,15 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="48">
+      <c r="C126" s="60">
         <v>25</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="50">
+      <c r="D126" s="61"/>
+      <c r="E126" s="62">
         <f t="shared" si="18"/>
         <v>25.105263157894736</v>
       </c>
-      <c r="F126" s="51"/>
+      <c r="F126" s="63"/>
       <c r="G126" s="35"/>
       <c r="I126" s="18">
         <f t="shared" si="17"/>
@@ -16014,15 +16022,15 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="48">
+      <c r="C127" s="60">
         <v>50</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="50">
+      <c r="D127" s="61"/>
+      <c r="E127" s="62">
         <f t="shared" si="18"/>
         <v>47.210526315789473</v>
       </c>
-      <c r="F127" s="51"/>
+      <c r="F127" s="63"/>
       <c r="G127" s="35"/>
       <c r="I127" s="18">
         <f t="shared" si="17"/>
@@ -16044,15 +16052,15 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="48">
+      <c r="C128" s="60">
         <v>100</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="50">
+      <c r="D128" s="61"/>
+      <c r="E128" s="62">
         <f t="shared" si="18"/>
         <v>95.631578947368425</v>
       </c>
-      <c r="F128" s="51"/>
+      <c r="F128" s="63"/>
       <c r="G128" s="35"/>
       <c r="I128" s="18">
         <f t="shared" si="17"/>
@@ -16074,15 +16082,15 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="48">
+      <c r="C129" s="60">
         <v>200</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="50">
+      <c r="D129" s="61"/>
+      <c r="E129" s="62">
         <f t="shared" si="18"/>
         <v>200.89473684210526</v>
       </c>
-      <c r="F129" s="51"/>
+      <c r="F129" s="63"/>
       <c r="G129" s="35"/>
       <c r="I129" s="18">
         <f t="shared" si="17"/>
@@ -16104,15 +16112,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="52">
+      <c r="C130" s="64">
         <v>500</v>
       </c>
-      <c r="D130" s="53"/>
-      <c r="E130" s="54">
+      <c r="D130" s="65"/>
+      <c r="E130" s="66">
         <f t="shared" si="18"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="55"/>
+      <c r="F130" s="67"/>
       <c r="G130" s="35"/>
       <c r="I130" s="19">
         <f t="shared" si="17"/>
@@ -16134,13 +16142,13 @@
       <c r="B131" s="4">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="62"/>
-      <c r="D131" s="63"/>
-      <c r="E131" s="64">
+      <c r="C131" s="74"/>
+      <c r="D131" s="75"/>
+      <c r="E131" s="76">
         <f t="shared" ref="E131:E138" si="21">(B131+0.0067)/0.0019</f>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="65"/>
+      <c r="F131" s="77"/>
       <c r="G131" s="35"/>
       <c r="I131" s="18">
         <f>E131/1000000</f>
@@ -16162,12 +16170,12 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="48"/>
-      <c r="D132" s="49"/>
-      <c r="E132" s="50">
+      <c r="C132" s="60"/>
+      <c r="D132" s="61"/>
+      <c r="E132" s="62">
         <v>0</v>
       </c>
-      <c r="F132" s="51"/>
+      <c r="F132" s="63"/>
       <c r="G132" s="35"/>
       <c r="I132" s="18">
         <f>E132/1000000</f>
@@ -16189,12 +16197,12 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="48"/>
-      <c r="D133" s="49"/>
-      <c r="E133" s="50">
+      <c r="C133" s="60"/>
+      <c r="D133" s="61"/>
+      <c r="E133" s="62">
         <v>0</v>
       </c>
-      <c r="F133" s="51"/>
+      <c r="F133" s="63"/>
       <c r="G133" s="35"/>
       <c r="I133" s="18">
         <f t="shared" ref="I133:I138" si="24">E133/1000000</f>
@@ -16216,12 +16224,12 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="48"/>
-      <c r="D134" s="49"/>
-      <c r="E134" s="50">
+      <c r="C134" s="60"/>
+      <c r="D134" s="61"/>
+      <c r="E134" s="62">
         <v>0</v>
       </c>
-      <c r="F134" s="51"/>
+      <c r="F134" s="63"/>
       <c r="G134" s="35"/>
       <c r="I134" s="18">
         <f t="shared" si="24"/>
@@ -16243,12 +16251,12 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="48"/>
-      <c r="D135" s="49"/>
-      <c r="E135" s="50">
+      <c r="C135" s="60"/>
+      <c r="D135" s="61"/>
+      <c r="E135" s="62">
         <v>0</v>
       </c>
-      <c r="F135" s="51"/>
+      <c r="F135" s="63"/>
       <c r="G135" s="35"/>
       <c r="I135" s="18">
         <f t="shared" si="24"/>
@@ -16270,13 +16278,13 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="48"/>
-      <c r="D136" s="49"/>
-      <c r="E136" s="50">
+      <c r="C136" s="60"/>
+      <c r="D136" s="61"/>
+      <c r="E136" s="62">
         <f t="shared" si="21"/>
         <v>13</v>
       </c>
-      <c r="F136" s="51"/>
+      <c r="F136" s="63"/>
       <c r="G136" s="35"/>
       <c r="I136" s="18">
         <f t="shared" si="24"/>
@@ -16298,13 +16306,13 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="48"/>
-      <c r="D137" s="49"/>
-      <c r="E137" s="50">
+      <c r="C137" s="60"/>
+      <c r="D137" s="61"/>
+      <c r="E137" s="62">
         <f t="shared" si="21"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="51"/>
+      <c r="F137" s="63"/>
       <c r="G137" s="35"/>
       <c r="I137" s="18">
         <f t="shared" si="24"/>
@@ -16326,13 +16334,13 @@
       <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="52"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="54">
+      <c r="C138" s="64"/>
+      <c r="D138" s="65"/>
+      <c r="E138" s="66">
         <f t="shared" si="21"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="55"/>
+      <c r="F138" s="67"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="24"/>
@@ -16459,16 +16467,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -16672,14 +16680,14 @@
         <v>34</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="77">
+      <c r="C55" s="89">
         <v>1</v>
       </c>
-      <c r="D55" s="77"/>
-      <c r="E55" s="68">
+      <c r="D55" s="89"/>
+      <c r="E55" s="80">
         <v>0</v>
       </c>
-      <c r="F55" s="69"/>
+      <c r="F55" s="81"/>
       <c r="H55" s="18"/>
       <c r="I55" s="27"/>
       <c r="J55" s="18"/>
@@ -16689,15 +16697,15 @@
         <v>35</v>
       </c>
       <c r="B56" s="6"/>
-      <c r="C56" s="76">
+      <c r="C56" s="88">
         <v>2.5</v>
       </c>
-      <c r="D56" s="76"/>
-      <c r="E56" s="57">
+      <c r="D56" s="88"/>
+      <c r="E56" s="69">
         <f t="shared" ref="E56" si="0">(B56-0.0164)/0.0093</f>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F56" s="58"/>
+      <c r="F56" s="70"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -16709,15 +16717,15 @@
       <c r="B57" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C57" s="76">
+      <c r="C57" s="88">
         <v>5</v>
       </c>
-      <c r="D57" s="76"/>
-      <c r="E57" s="57">
+      <c r="D57" s="88"/>
+      <c r="E57" s="69">
         <f>(B57-0.0164)/0.0093</f>
         <v>2.0000000000000004</v>
       </c>
-      <c r="F57" s="58"/>
+      <c r="F57" s="70"/>
       <c r="H57" s="18">
         <f>C57/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -16738,15 +16746,15 @@
       <c r="B58" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C58" s="76">
+      <c r="C58" s="88">
         <v>10</v>
       </c>
-      <c r="D58" s="76"/>
-      <c r="E58" s="50">
+      <c r="D58" s="88"/>
+      <c r="E58" s="62">
         <f t="shared" ref="E58:E62" si="1">(B58-0.0164)/0.0093</f>
         <v>7.1612903225806468</v>
       </c>
-      <c r="F58" s="51"/>
+      <c r="F58" s="63"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -16765,15 +16773,15 @@
         <v>36</v>
       </c>
       <c r="B59" s="6"/>
-      <c r="C59" s="76">
+      <c r="C59" s="88">
         <v>25</v>
       </c>
-      <c r="D59" s="76"/>
-      <c r="E59" s="50">
+      <c r="D59" s="88"/>
+      <c r="E59" s="62">
         <f t="shared" si="1"/>
         <v>-1.763440860215054</v>
       </c>
-      <c r="F59" s="51"/>
+      <c r="F59" s="63"/>
       <c r="H59" s="18"/>
       <c r="I59" s="18"/>
       <c r="J59" s="21"/>
@@ -16785,15 +16793,15 @@
       <c r="B60" s="6">
         <v>0.48499999999999999</v>
       </c>
-      <c r="C60" s="76">
+      <c r="C60" s="88">
         <v>50</v>
       </c>
-      <c r="D60" s="76"/>
-      <c r="E60" s="50">
+      <c r="D60" s="88"/>
+      <c r="E60" s="62">
         <f t="shared" si="1"/>
         <v>50.387096774193552</v>
       </c>
-      <c r="F60" s="51"/>
+      <c r="F60" s="63"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -16814,15 +16822,15 @@
       <c r="B61" s="6">
         <v>0.96499999999999997</v>
       </c>
-      <c r="C61" s="76">
+      <c r="C61" s="88">
         <v>100</v>
       </c>
-      <c r="D61" s="76"/>
-      <c r="E61" s="50">
+      <c r="D61" s="88"/>
+      <c r="E61" s="62">
         <f t="shared" si="1"/>
         <v>102.00000000000001</v>
       </c>
-      <c r="F61" s="51"/>
+      <c r="F61" s="63"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>1E-4</v>
@@ -16843,15 +16851,15 @@
       <c r="B62" s="8">
         <v>1.8340000000000001</v>
       </c>
-      <c r="C62" s="52">
+      <c r="C62" s="64">
         <v>200</v>
       </c>
-      <c r="D62" s="53"/>
-      <c r="E62" s="54">
+      <c r="D62" s="65"/>
+      <c r="E62" s="66">
         <f t="shared" si="1"/>
         <v>195.44086021505379</v>
       </c>
-      <c r="F62" s="55"/>
+      <c r="F62" s="67"/>
       <c r="H62" s="19">
         <f>C62/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -16872,12 +16880,12 @@
       <c r="B63" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C63" s="72"/>
-      <c r="D63" s="73"/>
-      <c r="E63" s="74">
+      <c r="C63" s="84"/>
+      <c r="D63" s="85"/>
+      <c r="E63" s="86">
         <v>0</v>
       </c>
-      <c r="F63" s="75"/>
+      <c r="F63" s="87"/>
       <c r="H63" s="18">
         <f t="shared" ref="H63:H70" si="4">E63/1000000</f>
         <v>0</v>
@@ -16898,12 +16906,12 @@
       <c r="B64" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C64" s="48"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="57">
+      <c r="C64" s="60"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="69">
         <v>0</v>
       </c>
-      <c r="F64" s="58"/>
+      <c r="F64" s="70"/>
       <c r="H64" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16924,12 +16932,12 @@
       <c r="B65" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="57">
+      <c r="C65" s="60"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="69">
         <v>0</v>
       </c>
-      <c r="F65" s="58"/>
+      <c r="F65" s="70"/>
       <c r="H65" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16950,12 +16958,12 @@
       <c r="B66" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="48"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="57">
+      <c r="C66" s="60"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="69">
         <v>0</v>
       </c>
-      <c r="F66" s="58"/>
+      <c r="F66" s="70"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -16976,13 +16984,13 @@
       <c r="B67" s="6">
         <v>0.109</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="57">
+      <c r="C67" s="60"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="69">
         <f t="shared" ref="E67:E70" si="7">(B67-0.0164)/0.0093</f>
         <v>9.9569892473118298</v>
       </c>
-      <c r="F67" s="58"/>
+      <c r="F67" s="70"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>9.9569892473118294E-6</v>
@@ -17003,13 +17011,13 @@
       <c r="B68" s="6">
         <v>0.36</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="57">
+      <c r="C68" s="60"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="69">
         <f t="shared" si="7"/>
         <v>36.946236559139784</v>
       </c>
-      <c r="F68" s="58"/>
+      <c r="F68" s="70"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>3.6946236559139785E-5</v>
@@ -17030,13 +17038,13 @@
       <c r="B69" s="6">
         <v>0.91300000000000003</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="57">
+      <c r="C69" s="60"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="69">
         <f t="shared" si="7"/>
         <v>96.408602150537646</v>
       </c>
-      <c r="F69" s="58"/>
+      <c r="F69" s="70"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>9.6408602150537646E-5</v>
@@ -17057,13 +17065,13 @@
       <c r="B70" s="8">
         <v>4.7E-2</v>
       </c>
-      <c r="C70" s="52"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="60">
+      <c r="C70" s="64"/>
+      <c r="D70" s="71"/>
+      <c r="E70" s="72">
         <f t="shared" si="7"/>
         <v>3.2903225806451615</v>
       </c>
-      <c r="F70" s="61"/>
+      <c r="F70" s="73"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>3.2903225806451615E-6</v>
@@ -17148,11 +17156,11 @@
         <v>0.5</v>
       </c>
       <c r="D101" s="11"/>
-      <c r="E101" s="68">
+      <c r="E101" s="80">
         <f>(B101+0.0049)/0.0204</f>
         <v>0.28921568627450978</v>
       </c>
-      <c r="F101" s="69"/>
+      <c r="F101" s="81"/>
       <c r="I101" s="16">
         <f t="shared" ref="I101:I106" si="8">C101/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -17177,11 +17185,11 @@
         <v>1</v>
       </c>
       <c r="D102" s="13"/>
-      <c r="E102" s="57">
+      <c r="E102" s="69">
         <f t="shared" ref="E102:E114" si="10">(B102+0.0049)/0.0204</f>
         <v>1.0245098039215685</v>
       </c>
-      <c r="F102" s="58"/>
+      <c r="F102" s="70"/>
       <c r="I102" s="18">
         <f t="shared" si="8"/>
         <v>9.9999999999999995E-7</v>
@@ -17206,11 +17214,11 @@
         <v>5</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="57">
+      <c r="E103" s="69">
         <f t="shared" si="10"/>
         <v>4.6029411764705879</v>
       </c>
-      <c r="F103" s="58"/>
+      <c r="F103" s="70"/>
       <c r="I103" s="18">
         <f t="shared" si="8"/>
         <v>5.0000000000000004E-6</v>
@@ -17235,11 +17243,11 @@
         <v>10</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="57">
+      <c r="E104" s="69">
         <f t="shared" si="10"/>
         <v>10.877450980392155</v>
       </c>
-      <c r="F104" s="58"/>
+      <c r="F104" s="70"/>
       <c r="I104" s="18">
         <f t="shared" si="8"/>
         <v>1.0000000000000001E-5</v>
@@ -17264,11 +17272,11 @@
         <v>25</v>
       </c>
       <c r="D105" s="33"/>
-      <c r="E105" s="57">
+      <c r="E105" s="69">
         <f t="shared" si="10"/>
         <v>24.799019607843135</v>
       </c>
-      <c r="F105" s="58"/>
+      <c r="F105" s="70"/>
       <c r="I105" s="18">
         <f t="shared" si="8"/>
         <v>2.5000000000000001E-5</v>
@@ -17293,11 +17301,11 @@
         <v>50</v>
       </c>
       <c r="D106" s="15"/>
-      <c r="E106" s="60">
+      <c r="E106" s="72">
         <f t="shared" si="10"/>
         <v>37.446078431372548</v>
       </c>
-      <c r="F106" s="61"/>
+      <c r="F106" s="73"/>
       <c r="I106" s="19">
         <f t="shared" si="8"/>
         <v>5.0000000000000002E-5</v>
@@ -17318,13 +17326,13 @@
       <c r="B107" s="9">
         <v>0</v>
       </c>
-      <c r="C107" s="72"/>
-      <c r="D107" s="73"/>
-      <c r="E107" s="74">
+      <c r="C107" s="84"/>
+      <c r="D107" s="85"/>
+      <c r="E107" s="86">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F107" s="75"/>
+      <c r="F107" s="87"/>
       <c r="I107" s="18">
         <f>E107/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -17345,13 +17353,13 @@
       <c r="B108" s="6">
         <v>0</v>
       </c>
-      <c r="C108" s="48"/>
-      <c r="D108" s="56"/>
-      <c r="E108" s="57">
+      <c r="C108" s="60"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="69">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F108" s="58"/>
+      <c r="F108" s="70"/>
       <c r="I108" s="18">
         <f t="shared" ref="I108:I114" si="12">E108/1000000</f>
         <v>2.4019607843137255E-7</v>
@@ -17372,13 +17380,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="48"/>
-      <c r="D109" s="56"/>
-      <c r="E109" s="57">
+      <c r="C109" s="60"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="69">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F109" s="58"/>
+      <c r="F109" s="70"/>
       <c r="I109" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -17399,13 +17407,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="48"/>
-      <c r="D110" s="56"/>
-      <c r="E110" s="57">
+      <c r="C110" s="60"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="69">
         <f t="shared" si="10"/>
         <v>0.24019607843137253</v>
       </c>
-      <c r="F110" s="58"/>
+      <c r="F110" s="70"/>
       <c r="I110" s="18">
         <f t="shared" si="12"/>
         <v>2.4019607843137255E-7</v>
@@ -17426,13 +17434,13 @@
       <c r="B111" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="57">
+      <c r="C111" s="60"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="69">
         <f t="shared" si="10"/>
         <v>0.92647058823529405</v>
       </c>
-      <c r="F111" s="58"/>
+      <c r="F111" s="70"/>
       <c r="I111" s="18">
         <f t="shared" si="12"/>
         <v>9.2647058823529408E-7</v>
@@ -17453,13 +17461,13 @@
       <c r="B112" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C112" s="48"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="57">
+      <c r="C112" s="60"/>
+      <c r="D112" s="68"/>
+      <c r="E112" s="69">
         <f t="shared" si="10"/>
         <v>0.68137254901960775</v>
       </c>
-      <c r="F112" s="58"/>
+      <c r="F112" s="70"/>
       <c r="I112" s="18">
         <f t="shared" si="12"/>
         <v>6.8137254901960776E-7</v>
@@ -17480,13 +17488,13 @@
       <c r="B113" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C113" s="48"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="57">
+      <c r="C113" s="60"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69">
         <f t="shared" si="10"/>
         <v>2.1519607843137254</v>
       </c>
-      <c r="F113" s="58"/>
+      <c r="F113" s="70"/>
       <c r="I113" s="18">
         <f t="shared" si="12"/>
         <v>2.1519607843137253E-6</v>
@@ -17507,13 +17515,13 @@
       <c r="B114" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C114" s="52"/>
-      <c r="D114" s="59"/>
-      <c r="E114" s="60">
+      <c r="C114" s="64"/>
+      <c r="D114" s="71"/>
+      <c r="E114" s="72">
         <f t="shared" si="10"/>
         <v>0.53431372549019607</v>
       </c>
-      <c r="F114" s="61"/>
+      <c r="F114" s="73"/>
       <c r="I114" s="18">
         <f t="shared" si="12"/>
         <v>5.3431372549019611E-7</v>
@@ -17529,7 +17537,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -17545,16 +17553,16 @@
       </c>
     </row>
     <row r="120" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="70" t="s">
+      <c r="A120" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B120" s="70"/>
-      <c r="C120" s="70"/>
-      <c r="D120" s="70"/>
-      <c r="E120" s="70"/>
-      <c r="F120" s="70"/>
-      <c r="G120" s="70"/>
-      <c r="H120" s="70"/>
+      <c r="B120" s="82"/>
+      <c r="C120" s="82"/>
+      <c r="D120" s="82"/>
+      <c r="E120" s="82"/>
+      <c r="F120" s="82"/>
+      <c r="G120" s="82"/>
+      <c r="H120" s="82"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I121" s="16" t="s">
@@ -17600,14 +17608,14 @@
       <c r="B123" s="4">
         <v>0</v>
       </c>
-      <c r="C123" s="62">
+      <c r="C123" s="74">
         <v>2.5</v>
       </c>
-      <c r="D123" s="63"/>
-      <c r="E123" s="68">
+      <c r="D123" s="75"/>
+      <c r="E123" s="80">
         <v>0</v>
       </c>
-      <c r="F123" s="69"/>
+      <c r="F123" s="81"/>
       <c r="G123" s="35"/>
       <c r="I123" s="16">
         <f t="shared" ref="I123:I130" si="15">C123/1000000</f>
@@ -17629,15 +17637,15 @@
       <c r="B124" s="2">
         <v>1E-3</v>
       </c>
-      <c r="C124" s="66">
+      <c r="C124" s="78">
         <v>5</v>
       </c>
-      <c r="D124" s="67"/>
-      <c r="E124" s="50">
+      <c r="D124" s="79"/>
+      <c r="E124" s="62">
         <f t="shared" ref="E124:E138" si="16">(B124+0.0067)/0.0019</f>
         <v>4.0526315789473681</v>
       </c>
-      <c r="F124" s="51"/>
+      <c r="F124" s="63"/>
       <c r="G124" s="35"/>
       <c r="I124" s="18">
         <f t="shared" si="15"/>
@@ -17659,15 +17667,15 @@
       <c r="B125" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C125" s="48">
+      <c r="C125" s="60">
         <v>10</v>
       </c>
-      <c r="D125" s="49"/>
-      <c r="E125" s="50">
+      <c r="D125" s="61"/>
+      <c r="E125" s="62">
         <f t="shared" si="16"/>
         <v>7.7368421052631584</v>
       </c>
-      <c r="F125" s="51"/>
+      <c r="F125" s="63"/>
       <c r="G125" s="35"/>
       <c r="I125" s="18">
         <f t="shared" si="15"/>
@@ -17689,15 +17697,15 @@
       <c r="B126" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C126" s="48">
+      <c r="C126" s="60">
         <v>25</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="50">
+      <c r="D126" s="61"/>
+      <c r="E126" s="62">
         <f t="shared" si="16"/>
         <v>25.105263157894736</v>
       </c>
-      <c r="F126" s="51"/>
+      <c r="F126" s="63"/>
       <c r="G126" s="35"/>
       <c r="I126" s="18">
         <f t="shared" si="15"/>
@@ -17719,15 +17727,15 @@
       <c r="B127" s="6">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="C127" s="48">
+      <c r="C127" s="60">
         <v>50</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="50">
+      <c r="D127" s="61"/>
+      <c r="E127" s="62">
         <f t="shared" si="16"/>
         <v>47.210526315789473</v>
       </c>
-      <c r="F127" s="51"/>
+      <c r="F127" s="63"/>
       <c r="G127" s="35"/>
       <c r="I127" s="18">
         <f t="shared" si="15"/>
@@ -17749,15 +17757,15 @@
       <c r="B128" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="C128" s="48">
+      <c r="C128" s="60">
         <v>100</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="50">
+      <c r="D128" s="61"/>
+      <c r="E128" s="62">
         <f t="shared" si="16"/>
         <v>95.631578947368425</v>
       </c>
-      <c r="F128" s="51"/>
+      <c r="F128" s="63"/>
       <c r="G128" s="35"/>
       <c r="I128" s="18">
         <f t="shared" si="15"/>
@@ -17779,15 +17787,15 @@
       <c r="B129" s="6">
         <v>0.375</v>
       </c>
-      <c r="C129" s="48">
+      <c r="C129" s="60">
         <v>200</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="50">
+      <c r="D129" s="61"/>
+      <c r="E129" s="62">
         <f t="shared" si="16"/>
         <v>200.89473684210526</v>
       </c>
-      <c r="F129" s="51"/>
+      <c r="F129" s="63"/>
       <c r="G129" s="35"/>
       <c r="I129" s="18">
         <f t="shared" si="15"/>
@@ -17809,15 +17817,15 @@
       <c r="B130" s="8">
         <v>0.91500000000000004</v>
       </c>
-      <c r="C130" s="52">
+      <c r="C130" s="64">
         <v>500</v>
       </c>
-      <c r="D130" s="53"/>
-      <c r="E130" s="54">
+      <c r="D130" s="65"/>
+      <c r="E130" s="66">
         <f t="shared" si="16"/>
         <v>485.1052631578948</v>
       </c>
-      <c r="F130" s="55"/>
+      <c r="F130" s="67"/>
       <c r="G130" s="35"/>
       <c r="I130" s="19">
         <f t="shared" si="15"/>
@@ -17839,13 +17847,13 @@
       <c r="B131" s="9">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C131" s="72"/>
-      <c r="D131" s="78"/>
-      <c r="E131" s="64">
+      <c r="C131" s="84"/>
+      <c r="D131" s="90"/>
+      <c r="E131" s="76">
         <f t="shared" si="16"/>
         <v>9.3157894736842106</v>
       </c>
-      <c r="F131" s="65"/>
+      <c r="F131" s="77"/>
       <c r="G131" s="35"/>
       <c r="I131" s="18">
         <f>E131/1000000</f>
@@ -17867,12 +17875,12 @@
       <c r="B132" s="6">
         <v>0</v>
       </c>
-      <c r="C132" s="48"/>
-      <c r="D132" s="49"/>
-      <c r="E132" s="50">
+      <c r="C132" s="60"/>
+      <c r="D132" s="61"/>
+      <c r="E132" s="62">
         <v>0</v>
       </c>
-      <c r="F132" s="51"/>
+      <c r="F132" s="63"/>
       <c r="G132" s="35"/>
       <c r="I132" s="18">
         <f>E132/1000000</f>
@@ -17894,12 +17902,12 @@
       <c r="B133" s="6">
         <v>0</v>
       </c>
-      <c r="C133" s="48"/>
-      <c r="D133" s="49"/>
-      <c r="E133" s="50">
+      <c r="C133" s="60"/>
+      <c r="D133" s="61"/>
+      <c r="E133" s="62">
         <v>0</v>
       </c>
-      <c r="F133" s="51"/>
+      <c r="F133" s="63"/>
       <c r="G133" s="35"/>
       <c r="I133" s="18">
         <f t="shared" ref="I133:I138" si="21">E133/1000000</f>
@@ -17921,12 +17929,12 @@
       <c r="B134" s="6">
         <v>0</v>
       </c>
-      <c r="C134" s="48"/>
-      <c r="D134" s="49"/>
-      <c r="E134" s="50">
+      <c r="C134" s="60"/>
+      <c r="D134" s="61"/>
+      <c r="E134" s="62">
         <v>0</v>
       </c>
-      <c r="F134" s="51"/>
+      <c r="F134" s="63"/>
       <c r="G134" s="35"/>
       <c r="I134" s="18">
         <f t="shared" si="21"/>
@@ -17948,12 +17956,12 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="48"/>
-      <c r="D135" s="49"/>
-      <c r="E135" s="50">
+      <c r="C135" s="60"/>
+      <c r="D135" s="61"/>
+      <c r="E135" s="62">
         <v>0</v>
       </c>
-      <c r="F135" s="51"/>
+      <c r="F135" s="63"/>
       <c r="G135" s="35"/>
       <c r="I135" s="18">
         <f t="shared" si="21"/>
@@ -17975,13 +17983,13 @@
       <c r="B136" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C136" s="48"/>
-      <c r="D136" s="49"/>
-      <c r="E136" s="50">
+      <c r="C136" s="60"/>
+      <c r="D136" s="61"/>
+      <c r="E136" s="62">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
-      <c r="F136" s="51"/>
+      <c r="F136" s="63"/>
       <c r="G136" s="35"/>
       <c r="I136" s="18">
         <f t="shared" si="21"/>
@@ -18003,13 +18011,13 @@
       <c r="B137" s="6">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="C137" s="48"/>
-      <c r="D137" s="49"/>
-      <c r="E137" s="50">
+      <c r="C137" s="60"/>
+      <c r="D137" s="61"/>
+      <c r="E137" s="62">
         <f t="shared" si="16"/>
         <v>18.263157894736842</v>
       </c>
-      <c r="F137" s="51"/>
+      <c r="F137" s="63"/>
       <c r="G137" s="35"/>
       <c r="I137" s="18">
         <f t="shared" si="21"/>
@@ -18031,13 +18039,13 @@
       <c r="B138" s="8">
         <v>2.7E-2</v>
       </c>
-      <c r="C138" s="52"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="54">
+      <c r="C138" s="64"/>
+      <c r="D138" s="65"/>
+      <c r="E138" s="66">
         <f t="shared" si="16"/>
         <v>17.736842105263158</v>
       </c>
-      <c r="F138" s="55"/>
+      <c r="F138" s="67"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="21"/>
@@ -18164,16 +18172,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -18382,14 +18390,14 @@
         <v>34</v>
       </c>
       <c r="B56" s="4"/>
-      <c r="C56" s="77">
+      <c r="C56" s="89">
         <v>1</v>
       </c>
-      <c r="D56" s="77"/>
-      <c r="E56" s="68">
+      <c r="D56" s="89"/>
+      <c r="E56" s="80">
         <v>0</v>
       </c>
-      <c r="F56" s="69"/>
+      <c r="F56" s="81"/>
       <c r="H56" s="18"/>
       <c r="I56" s="27"/>
       <c r="J56" s="18"/>
@@ -18399,15 +18407,15 @@
         <v>35</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="76">
+      <c r="C57" s="88">
         <v>2.5</v>
       </c>
-      <c r="D57" s="76"/>
-      <c r="E57" s="57">
+      <c r="D57" s="88"/>
+      <c r="E57" s="69">
         <f>(B57+0.0048)/0.0096</f>
         <v>0.5</v>
       </c>
-      <c r="F57" s="58"/>
+      <c r="F57" s="70"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -18419,15 +18427,15 @@
       <c r="B58" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C58" s="76">
+      <c r="C58" s="88">
         <v>5</v>
       </c>
-      <c r="D58" s="76"/>
-      <c r="E58" s="57">
+      <c r="D58" s="88"/>
+      <c r="E58" s="69">
         <f>(B58+0.0048)/0.0096</f>
         <v>4.25</v>
       </c>
-      <c r="F58" s="58"/>
+      <c r="F58" s="70"/>
       <c r="H58" s="18">
         <f>C58/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -18448,15 +18456,15 @@
       <c r="B59" s="6">
         <v>0.08</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="88">
         <v>10</v>
       </c>
-      <c r="D59" s="76"/>
-      <c r="E59" s="57">
+      <c r="D59" s="88"/>
+      <c r="E59" s="69">
         <f t="shared" ref="E59:E62" si="0">(B59+0.0048)/0.0096</f>
         <v>8.8333333333333339</v>
       </c>
-      <c r="F59" s="58"/>
+      <c r="F59" s="70"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -18475,15 +18483,15 @@
         <v>36</v>
       </c>
       <c r="B60" s="6"/>
-      <c r="C60" s="76">
+      <c r="C60" s="88">
         <v>25</v>
       </c>
-      <c r="D60" s="76"/>
-      <c r="E60" s="57">
+      <c r="D60" s="88"/>
+      <c r="E60" s="69">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F60" s="58"/>
+      <c r="F60" s="70"/>
       <c r="H60" s="18"/>
       <c r="I60" s="18"/>
       <c r="J60" s="21"/>
@@ -18495,15 +18503,15 @@
       <c r="B61" s="6">
         <v>0.48399999999999999</v>
       </c>
-      <c r="C61" s="76">
+      <c r="C61" s="88">
         <v>50</v>
       </c>
-      <c r="D61" s="76"/>
-      <c r="E61" s="57">
+      <c r="D61" s="88"/>
+      <c r="E61" s="69">
         <f t="shared" si="0"/>
         <v>50.916666666666671</v>
       </c>
-      <c r="F61" s="58"/>
+      <c r="F61" s="70"/>
       <c r="H61" s="18">
         <f>C61/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -18524,15 +18532,15 @@
       <c r="B62" s="6">
         <v>0.97299999999999998</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="88">
         <v>100</v>
       </c>
-      <c r="D62" s="76"/>
-      <c r="E62" s="57">
+      <c r="D62" s="88"/>
+      <c r="E62" s="69">
         <f t="shared" si="0"/>
         <v>101.85416666666667</v>
       </c>
-      <c r="F62" s="58"/>
+      <c r="F62" s="70"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>1E-4</v>
@@ -18553,15 +18561,15 @@
       <c r="B63" s="8">
         <v>1.899</v>
       </c>
-      <c r="C63" s="52">
+      <c r="C63" s="64">
         <v>200</v>
       </c>
-      <c r="D63" s="53"/>
-      <c r="E63" s="60">
+      <c r="D63" s="65"/>
+      <c r="E63" s="72">
         <f t="shared" ref="E63" si="3">(B63+0.0048)/0.0096</f>
         <v>198.3125</v>
       </c>
-      <c r="F63" s="61"/>
+      <c r="F63" s="73"/>
       <c r="H63" s="19">
         <f>C63/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -18582,13 +18590,13 @@
       <c r="B64" s="9">
         <v>1.25</v>
       </c>
-      <c r="C64" s="72"/>
-      <c r="D64" s="73"/>
-      <c r="E64" s="74">
+      <c r="C64" s="84"/>
+      <c r="D64" s="85"/>
+      <c r="E64" s="86">
         <f t="shared" ref="E64" si="4">(B64+0.0048)/0.0096</f>
         <v>130.70833333333334</v>
       </c>
-      <c r="F64" s="75"/>
+      <c r="F64" s="87"/>
       <c r="H64" s="18">
         <f t="shared" ref="H64:H71" si="5">E64/1000000</f>
         <v>1.3070833333333334E-4</v>
@@ -18609,13 +18617,13 @@
       <c r="B65" s="6">
         <v>1E-3</v>
       </c>
-      <c r="C65" s="48"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="74">
+      <c r="C65" s="60"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="86">
         <f t="shared" ref="E65:E71" si="6">(B65+0.0048)/0.0096</f>
         <v>0.60416666666666663</v>
       </c>
-      <c r="F65" s="75"/>
+      <c r="F65" s="87"/>
       <c r="H65" s="18">
         <f t="shared" si="5"/>
         <v>6.0416666666666667E-7</v>
@@ -18636,13 +18644,13 @@
       <c r="B66" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="C66" s="48"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="74">
+      <c r="C66" s="60"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="86">
         <f t="shared" si="6"/>
         <v>1.0208333333333335</v>
       </c>
-      <c r="F66" s="75"/>
+      <c r="F66" s="87"/>
       <c r="H66" s="18">
         <f t="shared" si="5"/>
         <v>1.0208333333333334E-6</v>
@@ -18663,13 +18671,13 @@
       <c r="B67" s="6">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="74">
+      <c r="C67" s="60"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="86">
         <f t="shared" si="6"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="F67" s="75"/>
+      <c r="F67" s="87"/>
       <c r="H67" s="18">
         <f t="shared" si="5"/>
         <v>1.3333333333333332E-6</v>
@@ -18690,13 +18698,13 @@
       <c r="B68" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="74">
+      <c r="C68" s="60"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="86">
         <f t="shared" si="6"/>
         <v>1.9583333333333335</v>
       </c>
-      <c r="F68" s="75"/>
+      <c r="F68" s="87"/>
       <c r="H68" s="18">
         <f t="shared" si="5"/>
         <v>1.9583333333333334E-6</v>
@@ -18717,13 +18725,13 @@
       <c r="B69" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="74">
+      <c r="C69" s="60"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="86">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="F69" s="75"/>
+      <c r="F69" s="87"/>
       <c r="H69" s="18">
         <f t="shared" si="5"/>
         <v>3.0000000000000001E-6</v>
@@ -18744,13 +18752,13 @@
       <c r="B70" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C70" s="48"/>
-      <c r="D70" s="56"/>
-      <c r="E70" s="74">
+      <c r="C70" s="60"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="86">
         <f t="shared" si="6"/>
         <v>4.7708333333333339</v>
       </c>
-      <c r="F70" s="75"/>
+      <c r="F70" s="87"/>
       <c r="H70" s="18">
         <f t="shared" si="5"/>
         <v>4.7708333333333335E-6</v>
@@ -18771,13 +18779,13 @@
       <c r="B71" s="8">
         <v>0.311</v>
       </c>
-      <c r="C71" s="52"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="81">
+      <c r="C71" s="64"/>
+      <c r="D71" s="71"/>
+      <c r="E71" s="93">
         <f t="shared" si="6"/>
         <v>32.895833333333336</v>
       </c>
-      <c r="F71" s="82"/>
+      <c r="F71" s="94"/>
       <c r="H71" s="18">
         <f t="shared" si="5"/>
         <v>3.2895833333333338E-5</v>
@@ -18862,11 +18870,11 @@
         <v>0.5</v>
       </c>
       <c r="D102" s="11"/>
-      <c r="E102" s="68">
+      <c r="E102" s="80">
         <f>(B102+0.001)/0.0211</f>
         <v>0.56872037914691942</v>
       </c>
-      <c r="F102" s="69"/>
+      <c r="F102" s="81"/>
       <c r="I102" s="16">
         <f t="shared" ref="I102:I107" si="9">C102/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -18891,11 +18899,11 @@
         <v>1</v>
       </c>
       <c r="D103" s="13"/>
-      <c r="E103" s="57">
+      <c r="E103" s="69">
         <f t="shared" ref="E103:E107" si="11">(B103+0.001)/0.0211</f>
         <v>1.0426540284360191</v>
       </c>
-      <c r="F103" s="58"/>
+      <c r="F103" s="70"/>
       <c r="I103" s="18">
         <f t="shared" si="9"/>
         <v>9.9999999999999995E-7</v>
@@ -18920,11 +18928,11 @@
         <v>5</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="57">
+      <c r="E104" s="69">
         <f t="shared" si="11"/>
         <v>5.0236966824644549</v>
       </c>
-      <c r="F104" s="58"/>
+      <c r="F104" s="70"/>
       <c r="I104" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000004E-6</v>
@@ -18949,11 +18957,11 @@
         <v>10</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="57">
+      <c r="E105" s="69">
         <f t="shared" si="11"/>
         <v>10.284360189573459</v>
       </c>
-      <c r="F105" s="58"/>
+      <c r="F105" s="70"/>
       <c r="I105" s="18">
         <f t="shared" si="9"/>
         <v>1.0000000000000001E-5</v>
@@ -18978,11 +18986,11 @@
         <v>25</v>
       </c>
       <c r="D106" s="33"/>
-      <c r="E106" s="57">
+      <c r="E106" s="69">
         <f t="shared" si="11"/>
         <v>24.976303317535546</v>
       </c>
-      <c r="F106" s="58"/>
+      <c r="F106" s="70"/>
       <c r="I106" s="19">
         <f t="shared" si="9"/>
         <v>2.5000000000000001E-5</v>
@@ -19007,11 +19015,11 @@
         <v>50</v>
       </c>
       <c r="D107" s="15"/>
-      <c r="E107" s="60">
+      <c r="E107" s="72">
         <f t="shared" si="11"/>
         <v>78.436018957345965</v>
       </c>
-      <c r="F107" s="61"/>
+      <c r="F107" s="73"/>
       <c r="I107" s="18">
         <f t="shared" si="9"/>
         <v>5.0000000000000002E-5</v>
@@ -19032,13 +19040,13 @@
       <c r="B108" s="9">
         <v>0</v>
       </c>
-      <c r="C108" s="72"/>
-      <c r="D108" s="73"/>
-      <c r="E108" s="74">
+      <c r="C108" s="84"/>
+      <c r="D108" s="85"/>
+      <c r="E108" s="86">
         <f t="shared" ref="E108:E115" si="13">(B108+0.001)/0.0211</f>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F108" s="75"/>
+      <c r="F108" s="87"/>
       <c r="I108" s="18">
         <f>E108/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -19059,13 +19067,13 @@
       <c r="B109" s="6">
         <v>0</v>
       </c>
-      <c r="C109" s="48"/>
-      <c r="D109" s="56"/>
-      <c r="E109" s="57">
+      <c r="C109" s="60"/>
+      <c r="D109" s="68"/>
+      <c r="E109" s="69">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F109" s="58"/>
+      <c r="F109" s="70"/>
       <c r="I109" s="18">
         <f t="shared" ref="I109:I115" si="14">E109/1000000</f>
         <v>4.7393364928909948E-8</v>
@@ -19086,13 +19094,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="48"/>
-      <c r="D110" s="56"/>
-      <c r="E110" s="57">
+      <c r="C110" s="60"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="69">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F110" s="58"/>
+      <c r="F110" s="70"/>
       <c r="I110" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -19113,13 +19121,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="57">
+      <c r="C111" s="60"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="69">
         <f t="shared" si="13"/>
         <v>4.7393364928909949E-2</v>
       </c>
-      <c r="F111" s="58"/>
+      <c r="F111" s="70"/>
       <c r="I111" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909948E-8</v>
@@ -19140,13 +19148,13 @@
       <c r="B112" s="6">
         <v>1.4E-2</v>
       </c>
-      <c r="C112" s="48"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="57">
+      <c r="C112" s="60"/>
+      <c r="D112" s="68"/>
+      <c r="E112" s="69">
         <f t="shared" si="13"/>
         <v>0.71090047393364919</v>
       </c>
-      <c r="F112" s="58"/>
+      <c r="F112" s="70"/>
       <c r="I112" s="18">
         <f t="shared" si="14"/>
         <v>7.1090047393364923E-7</v>
@@ -19167,13 +19175,13 @@
       <c r="B113" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C113" s="48"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="57">
+      <c r="C113" s="60"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69">
         <f t="shared" si="13"/>
         <v>0.47393364928909942</v>
       </c>
-      <c r="F113" s="58"/>
+      <c r="F113" s="70"/>
       <c r="I113" s="18">
         <f t="shared" si="14"/>
         <v>4.7393364928909945E-7</v>
@@ -19194,13 +19202,13 @@
       <c r="B114" s="6">
         <v>3.9E-2</v>
       </c>
-      <c r="C114" s="48"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="57">
+      <c r="C114" s="60"/>
+      <c r="D114" s="68"/>
+      <c r="E114" s="69">
         <f t="shared" si="13"/>
         <v>1.8957345971563981</v>
       </c>
-      <c r="F114" s="58"/>
+      <c r="F114" s="70"/>
       <c r="I114" s="18">
         <f t="shared" si="14"/>
         <v>1.8957345971563982E-6</v>
@@ -19221,13 +19229,13 @@
       <c r="B115" s="8">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C115" s="52"/>
-      <c r="D115" s="59"/>
-      <c r="E115" s="60">
+      <c r="C115" s="64"/>
+      <c r="D115" s="71"/>
+      <c r="E115" s="72">
         <f t="shared" si="13"/>
         <v>0.33175355450236965</v>
       </c>
-      <c r="F115" s="61"/>
+      <c r="F115" s="73"/>
       <c r="I115" s="18">
         <f t="shared" si="14"/>
         <v>3.3175355450236965E-7</v>
@@ -19243,7 +19251,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I118" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K118">
         <v>62.005400000000002</v>
@@ -19261,16 +19269,16 @@
       <c r="H120" s="24"/>
     </row>
     <row r="121" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="70" t="s">
+      <c r="A121" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B121" s="70"/>
-      <c r="C121" s="70"/>
-      <c r="D121" s="70"/>
-      <c r="E121" s="70"/>
-      <c r="F121" s="70"/>
-      <c r="G121" s="70"/>
-      <c r="H121" s="70"/>
+      <c r="B121" s="82"/>
+      <c r="C121" s="82"/>
+      <c r="D121" s="82"/>
+      <c r="E121" s="82"/>
+      <c r="F121" s="82"/>
+      <c r="G121" s="82"/>
+      <c r="H121" s="82"/>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I122" s="16" t="s">
@@ -19314,14 +19322,14 @@
         <v>56</v>
       </c>
       <c r="B124" s="4"/>
-      <c r="C124" s="62">
+      <c r="C124" s="74">
         <v>2.5</v>
       </c>
-      <c r="D124" s="63"/>
-      <c r="E124" s="68">
+      <c r="D124" s="75"/>
+      <c r="E124" s="80">
         <v>0</v>
       </c>
-      <c r="F124" s="69"/>
+      <c r="F124" s="81"/>
       <c r="G124" s="35"/>
       <c r="I124" s="16">
         <f t="shared" ref="I124:I131" si="17">C124/1000000</f>
@@ -19341,15 +19349,15 @@
         <v>11</v>
       </c>
       <c r="B125" s="2"/>
-      <c r="C125" s="66">
+      <c r="C125" s="78">
         <v>5</v>
       </c>
-      <c r="D125" s="67"/>
-      <c r="E125" s="50">
+      <c r="D125" s="79"/>
+      <c r="E125" s="62">
         <f>(B125+0.0053)/0.0019</f>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F125" s="51"/>
+      <c r="F125" s="63"/>
       <c r="G125" s="35"/>
       <c r="I125" s="18">
         <f t="shared" si="17"/>
@@ -19371,15 +19379,15 @@
       <c r="B126" s="6">
         <v>2.3E-2</v>
       </c>
-      <c r="C126" s="48">
+      <c r="C126" s="60">
         <v>10</v>
       </c>
-      <c r="D126" s="49"/>
-      <c r="E126" s="50">
+      <c r="D126" s="61"/>
+      <c r="E126" s="62">
         <f t="shared" ref="E126:E131" si="20">(B126+0.0053)/0.0019</f>
         <v>14.894736842105262</v>
       </c>
-      <c r="F126" s="51"/>
+      <c r="F126" s="63"/>
       <c r="G126" s="35"/>
       <c r="I126" s="18">
         <f t="shared" si="17"/>
@@ -19399,15 +19407,15 @@
         <v>12</v>
       </c>
       <c r="B127" s="6"/>
-      <c r="C127" s="48">
+      <c r="C127" s="60">
         <v>25</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="50">
+      <c r="D127" s="61"/>
+      <c r="E127" s="62">
         <f t="shared" si="20"/>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F127" s="51"/>
+      <c r="F127" s="63"/>
       <c r="G127" s="35"/>
       <c r="I127" s="18">
         <f t="shared" si="17"/>
@@ -19429,15 +19437,15 @@
       <c r="B128" s="6">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="C128" s="48">
+      <c r="C128" s="60">
         <v>50</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="50">
+      <c r="D128" s="61"/>
+      <c r="E128" s="62">
         <f t="shared" si="20"/>
         <v>53.315789473684212</v>
       </c>
-      <c r="F128" s="51"/>
+      <c r="F128" s="63"/>
       <c r="G128" s="35"/>
       <c r="I128" s="18">
         <f t="shared" si="17"/>
@@ -19459,15 +19467,15 @@
       <c r="B129" s="6">
         <v>0.20499999999999999</v>
       </c>
-      <c r="C129" s="48">
+      <c r="C129" s="60">
         <v>100</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="50">
+      <c r="D129" s="61"/>
+      <c r="E129" s="62">
         <f t="shared" si="20"/>
         <v>110.68421052631578</v>
       </c>
-      <c r="F129" s="51"/>
+      <c r="F129" s="63"/>
       <c r="G129" s="35"/>
       <c r="I129" s="18">
         <f t="shared" si="17"/>
@@ -19489,15 +19497,15 @@
       <c r="B130" s="6">
         <v>0.39500000000000002</v>
       </c>
-      <c r="C130" s="48">
+      <c r="C130" s="60">
         <v>200</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="50">
+      <c r="D130" s="61"/>
+      <c r="E130" s="62">
         <f t="shared" si="20"/>
         <v>210.68421052631581</v>
       </c>
-      <c r="F130" s="51"/>
+      <c r="F130" s="63"/>
       <c r="G130" s="35"/>
       <c r="I130" s="18">
         <f t="shared" si="17"/>
@@ -19519,15 +19527,15 @@
       <c r="B131" s="8">
         <v>0.97</v>
       </c>
-      <c r="C131" s="52">
+      <c r="C131" s="64">
         <v>500</v>
       </c>
-      <c r="D131" s="53"/>
-      <c r="E131" s="54">
+      <c r="D131" s="65"/>
+      <c r="E131" s="66">
         <f t="shared" si="20"/>
         <v>513.31578947368416</v>
       </c>
-      <c r="F131" s="55"/>
+      <c r="F131" s="67"/>
       <c r="G131" s="35"/>
       <c r="I131" s="19">
         <f t="shared" si="17"/>
@@ -19549,13 +19557,13 @@
       <c r="B132" s="9">
         <v>1.4E-2</v>
       </c>
-      <c r="C132" s="72"/>
-      <c r="D132" s="78"/>
-      <c r="E132" s="79">
+      <c r="C132" s="84"/>
+      <c r="D132" s="90"/>
+      <c r="E132" s="91">
         <f t="shared" ref="E132" si="21">(B132+0.0053)/0.0019</f>
         <v>10.157894736842106</v>
       </c>
-      <c r="F132" s="80"/>
+      <c r="F132" s="92"/>
       <c r="G132" s="35"/>
       <c r="I132" s="18">
         <f>E132/1000000</f>
@@ -19577,13 +19585,13 @@
       <c r="B133" s="6">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="48"/>
-      <c r="D133" s="49"/>
-      <c r="E133" s="50">
+      <c r="C133" s="60"/>
+      <c r="D133" s="61"/>
+      <c r="E133" s="62">
         <f t="shared" ref="E133" si="24">(B133+0.0053)/0.0019</f>
         <v>7.5263157894736841</v>
       </c>
-      <c r="F133" s="51"/>
+      <c r="F133" s="63"/>
       <c r="G133" s="35"/>
       <c r="I133" s="18">
         <f>E133/1000000</f>
@@ -19605,13 +19613,13 @@
       <c r="B134" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C134" s="48"/>
-      <c r="D134" s="49"/>
-      <c r="E134" s="50">
+      <c r="C134" s="60"/>
+      <c r="D134" s="61"/>
+      <c r="E134" s="62">
         <f t="shared" ref="E134:E139" si="25">(B134+0.0053)/0.0019</f>
         <v>3.8421052631578947</v>
       </c>
-      <c r="F134" s="51"/>
+      <c r="F134" s="63"/>
       <c r="G134" s="35"/>
       <c r="I134" s="18">
         <f t="shared" ref="I134:I139" si="26">E134/1000000</f>
@@ -19633,13 +19641,13 @@
       <c r="B135" s="6">
         <v>0</v>
       </c>
-      <c r="C135" s="48"/>
-      <c r="D135" s="49"/>
-      <c r="E135" s="50">
+      <c r="C135" s="60"/>
+      <c r="D135" s="61"/>
+      <c r="E135" s="62">
         <f t="shared" si="25"/>
         <v>2.7894736842105265</v>
       </c>
-      <c r="F135" s="51"/>
+      <c r="F135" s="63"/>
       <c r="G135" s="35"/>
       <c r="I135" s="18">
         <f t="shared" si="26"/>
@@ -19661,13 +19669,13 @@
       <c r="B136" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="48"/>
-      <c r="D136" s="49"/>
-      <c r="E136" s="50">
+      <c r="C136" s="60"/>
+      <c r="D136" s="61"/>
+      <c r="E136" s="62">
         <f t="shared" si="25"/>
         <v>5.9473684210526319</v>
       </c>
-      <c r="F136" s="51"/>
+      <c r="F136" s="63"/>
       <c r="G136" s="35"/>
       <c r="I136" s="18">
         <f t="shared" si="26"/>
@@ -19689,13 +19697,13 @@
       <c r="B137" s="6">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C137" s="48"/>
-      <c r="D137" s="49"/>
-      <c r="E137" s="50">
+      <c r="C137" s="60"/>
+      <c r="D137" s="61"/>
+      <c r="E137" s="62">
         <f t="shared" si="25"/>
         <v>15.947368421052632</v>
       </c>
-      <c r="F137" s="51"/>
+      <c r="F137" s="63"/>
       <c r="G137" s="35"/>
       <c r="I137" s="18">
         <f t="shared" si="26"/>
@@ -19717,13 +19725,13 @@
       <c r="B138" s="6">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="C138" s="48"/>
-      <c r="D138" s="49"/>
-      <c r="E138" s="50">
+      <c r="C138" s="60"/>
+      <c r="D138" s="61"/>
+      <c r="E138" s="62">
         <f t="shared" si="25"/>
         <v>9.6315789473684212</v>
       </c>
-      <c r="F138" s="51"/>
+      <c r="F138" s="63"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="26"/>
@@ -19745,13 +19753,13 @@
       <c r="B139" s="8">
         <v>1.4E-2</v>
       </c>
-      <c r="C139" s="52"/>
-      <c r="D139" s="53"/>
-      <c r="E139" s="54">
+      <c r="C139" s="64"/>
+      <c r="D139" s="65"/>
+      <c r="E139" s="66">
         <f t="shared" si="25"/>
         <v>10.157894736842106</v>
       </c>
-      <c r="F139" s="55"/>
+      <c r="F139" s="67"/>
       <c r="G139" s="35"/>
       <c r="I139" s="18">
         <f t="shared" si="26"/>
@@ -19878,16 +19886,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" s="25" customFormat="1" x14ac:dyDescent="0.25">
@@ -20102,14 +20110,14 @@
       <c r="B57" s="6">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C57" s="76">
+      <c r="C57" s="88">
         <v>1</v>
       </c>
-      <c r="D57" s="76"/>
-      <c r="E57" s="57">
+      <c r="D57" s="88"/>
+      <c r="E57" s="69">
         <v>0</v>
       </c>
-      <c r="F57" s="58"/>
+      <c r="F57" s="70"/>
       <c r="H57" s="18"/>
       <c r="I57" s="27"/>
       <c r="J57" s="18"/>
@@ -20121,15 +20129,15 @@
       <c r="B58" s="6">
         <v>1.7999999999999999E-2</v>
       </c>
-      <c r="C58" s="76">
+      <c r="C58" s="88">
         <v>2.5</v>
       </c>
-      <c r="D58" s="76"/>
-      <c r="E58" s="57">
+      <c r="D58" s="88"/>
+      <c r="E58" s="69">
         <f>(B58-0.0099)/0.0098</f>
         <v>0.82653061224489777</v>
       </c>
-      <c r="F58" s="58"/>
+      <c r="F58" s="70"/>
       <c r="H58" s="18"/>
       <c r="I58" s="27"/>
       <c r="J58" s="18"/>
@@ -20141,15 +20149,15 @@
       <c r="B59" s="6">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="88">
         <v>5</v>
       </c>
-      <c r="D59" s="76"/>
-      <c r="E59" s="57">
+      <c r="D59" s="88"/>
+      <c r="E59" s="69">
         <f t="shared" ref="E59:E64" si="0">(B59-0.0099)/0.0098</f>
         <v>3.3775510204081631</v>
       </c>
-      <c r="F59" s="58"/>
+      <c r="F59" s="70"/>
       <c r="H59" s="18">
         <f>C59/1000000</f>
         <v>5.0000000000000004E-6</v>
@@ -20170,15 +20178,15 @@
       <c r="B60" s="6">
         <v>9.4E-2</v>
       </c>
-      <c r="C60" s="76">
+      <c r="C60" s="88">
         <v>10</v>
       </c>
-      <c r="D60" s="76"/>
-      <c r="E60" s="57">
+      <c r="D60" s="88"/>
+      <c r="E60" s="69">
         <f t="shared" si="0"/>
         <v>8.5816326530612237</v>
       </c>
-      <c r="F60" s="58"/>
+      <c r="F60" s="70"/>
       <c r="H60" s="18">
         <f>C60/1000000</f>
         <v>1.0000000000000001E-5</v>
@@ -20199,15 +20207,15 @@
       <c r="B61" s="6">
         <v>0.25</v>
       </c>
-      <c r="C61" s="76">
+      <c r="C61" s="88">
         <v>25</v>
       </c>
-      <c r="D61" s="76"/>
-      <c r="E61" s="57">
+      <c r="D61" s="88"/>
+      <c r="E61" s="69">
         <f t="shared" si="0"/>
         <v>24.5</v>
       </c>
-      <c r="F61" s="58"/>
+      <c r="F61" s="70"/>
       <c r="H61" s="18"/>
       <c r="I61" s="18"/>
       <c r="J61" s="21"/>
@@ -20219,15 +20227,15 @@
       <c r="B62" s="6">
         <v>0.52</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="88">
         <v>50</v>
       </c>
-      <c r="D62" s="76"/>
-      <c r="E62" s="57">
+      <c r="D62" s="88"/>
+      <c r="E62" s="69">
         <f t="shared" si="0"/>
         <v>52.051020408163268</v>
       </c>
-      <c r="F62" s="58"/>
+      <c r="F62" s="70"/>
       <c r="H62" s="18">
         <f>C62/1000000</f>
         <v>5.0000000000000002E-5</v>
@@ -20248,15 +20256,15 @@
       <c r="B63" s="6">
         <v>1.028</v>
       </c>
-      <c r="C63" s="76">
+      <c r="C63" s="88">
         <v>100</v>
       </c>
-      <c r="D63" s="76"/>
-      <c r="E63" s="57">
+      <c r="D63" s="88"/>
+      <c r="E63" s="69">
         <f t="shared" si="0"/>
         <v>103.88775510204081</v>
       </c>
-      <c r="F63" s="58"/>
+      <c r="F63" s="70"/>
       <c r="H63" s="18">
         <f>C63/1000000</f>
         <v>1E-4</v>
@@ -20277,15 +20285,15 @@
       <c r="B64" s="8">
         <v>1.95</v>
       </c>
-      <c r="C64" s="52">
+      <c r="C64" s="64">
         <v>200</v>
       </c>
-      <c r="D64" s="53"/>
-      <c r="E64" s="57">
+      <c r="D64" s="65"/>
+      <c r="E64" s="69">
         <f t="shared" si="0"/>
         <v>197.96938775510205</v>
       </c>
-      <c r="F64" s="58"/>
+      <c r="F64" s="70"/>
       <c r="H64" s="19">
         <f>C64/1000000</f>
         <v>2.0000000000000001E-4</v>
@@ -20306,13 +20314,13 @@
       <c r="B65" s="9">
         <v>0.224</v>
       </c>
-      <c r="C65" s="72"/>
-      <c r="D65" s="73"/>
-      <c r="E65" s="57">
+      <c r="C65" s="84"/>
+      <c r="D65" s="85"/>
+      <c r="E65" s="69">
         <f t="shared" ref="E65:E73" si="3">(B65-0.0099)/0.0098</f>
         <v>21.846938775510207</v>
       </c>
-      <c r="F65" s="58"/>
+      <c r="F65" s="70"/>
       <c r="H65" s="18">
         <f t="shared" ref="H65:H73" si="4">E65/1000000</f>
         <v>2.1846938775510207E-5</v>
@@ -20333,13 +20341,13 @@
       <c r="B66" s="6">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="C66" s="48"/>
-      <c r="D66" s="56"/>
-      <c r="E66" s="57">
+      <c r="C66" s="60"/>
+      <c r="D66" s="68"/>
+      <c r="E66" s="69">
         <f t="shared" si="3"/>
         <v>1.9489795918367347</v>
       </c>
-      <c r="F66" s="58"/>
+      <c r="F66" s="70"/>
       <c r="H66" s="18">
         <f t="shared" si="4"/>
         <v>1.9489795918367348E-6</v>
@@ -20360,13 +20368,13 @@
       <c r="B67" s="6">
         <v>2.4E-2</v>
       </c>
-      <c r="C67" s="48"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="57">
+      <c r="C67" s="60"/>
+      <c r="D67" s="68"/>
+      <c r="E67" s="69">
         <f t="shared" si="3"/>
         <v>1.4387755102040816</v>
       </c>
-      <c r="F67" s="58"/>
+      <c r="F67" s="70"/>
       <c r="H67" s="18">
         <f t="shared" si="4"/>
         <v>1.4387755102040816E-6</v>
@@ -20387,13 +20395,13 @@
       <c r="B68" s="6">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="C68" s="48"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="57">
+      <c r="C68" s="60"/>
+      <c r="D68" s="68"/>
+      <c r="E68" s="69">
         <f t="shared" si="3"/>
         <v>7.0510204081632653</v>
       </c>
-      <c r="F68" s="58"/>
+      <c r="F68" s="70"/>
       <c r="H68" s="18">
         <f t="shared" si="4"/>
         <v>7.051020408163265E-6</v>
@@ -20414,13 +20422,13 @@
       <c r="B69" s="6">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="C69" s="48"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="57">
+      <c r="C69" s="60"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="69">
         <f t="shared" si="3"/>
         <v>3.1734693877551026</v>
       </c>
-      <c r="F69" s="58"/>
+      <c r="F69" s="70"/>
       <c r="H69" s="18">
         <f t="shared" si="4"/>
         <v>3.1734693877551026E-6</v>
@@ -20441,13 +20449,13 @@
       <c r="B70" s="6">
         <v>0.224</v>
       </c>
-      <c r="C70" s="48"/>
-      <c r="D70" s="56"/>
-      <c r="E70" s="57">
+      <c r="C70" s="60"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="69">
         <f t="shared" si="3"/>
         <v>21.846938775510207</v>
       </c>
-      <c r="F70" s="58"/>
+      <c r="F70" s="70"/>
       <c r="H70" s="18">
         <f t="shared" si="4"/>
         <v>2.1846938775510207E-5</v>
@@ -20468,13 +20476,13 @@
       <c r="B71" s="6">
         <v>0.221</v>
       </c>
-      <c r="C71" s="48"/>
-      <c r="D71" s="56"/>
-      <c r="E71" s="57">
+      <c r="C71" s="60"/>
+      <c r="D71" s="68"/>
+      <c r="E71" s="69">
         <f t="shared" si="3"/>
         <v>21.540816326530614</v>
       </c>
-      <c r="F71" s="58"/>
+      <c r="F71" s="70"/>
       <c r="H71" s="18">
         <f t="shared" si="4"/>
         <v>2.1540816326530614E-5</v>
@@ -20495,13 +20503,13 @@
       <c r="B72" s="6">
         <v>0.11700000000000001</v>
       </c>
-      <c r="C72" s="48"/>
-      <c r="D72" s="56"/>
-      <c r="E72" s="57">
+      <c r="C72" s="60"/>
+      <c r="D72" s="68"/>
+      <c r="E72" s="69">
         <f t="shared" si="3"/>
         <v>10.928571428571429</v>
       </c>
-      <c r="F72" s="58"/>
+      <c r="F72" s="70"/>
       <c r="H72" s="18">
         <f t="shared" si="4"/>
         <v>1.0928571428571429E-5</v>
@@ -20522,13 +20530,13 @@
       <c r="B73" s="6">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="C73" s="48"/>
-      <c r="D73" s="56"/>
-      <c r="E73" s="57">
+      <c r="C73" s="60"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="69">
         <f t="shared" si="3"/>
         <v>2.5612244897959191</v>
       </c>
-      <c r="F73" s="58"/>
+      <c r="F73" s="70"/>
       <c r="H73" s="18">
         <f t="shared" si="4"/>
         <v>2.5612244897959191E-6</v>
@@ -20613,11 +20621,11 @@
         <v>0.5</v>
       </c>
       <c r="D103" s="11"/>
-      <c r="E103" s="68">
+      <c r="E103" s="80">
         <f>(B103+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F103" s="69"/>
+      <c r="F103" s="81"/>
       <c r="I103" s="16">
         <f t="shared" ref="I103:I108" si="7">C103/1000000</f>
         <v>4.9999999999999998E-7</v>
@@ -20642,11 +20650,11 @@
         <v>1</v>
       </c>
       <c r="D104" s="13"/>
-      <c r="E104" s="57">
+      <c r="E104" s="69">
         <f t="shared" ref="E104:E108" si="9">(B104+0.001)/0.0201</f>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F104" s="58"/>
+      <c r="F104" s="70"/>
       <c r="I104" s="18">
         <f t="shared" si="7"/>
         <v>9.9999999999999995E-7</v>
@@ -20671,11 +20679,11 @@
         <v>5</v>
       </c>
       <c r="D105" s="13"/>
-      <c r="E105" s="57">
+      <c r="E105" s="69">
         <f t="shared" si="9"/>
         <v>4.1293532338308463</v>
       </c>
-      <c r="F105" s="58"/>
+      <c r="F105" s="70"/>
       <c r="I105" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000004E-6</v>
@@ -20700,11 +20708,11 @@
         <v>10</v>
       </c>
       <c r="D106" s="13"/>
-      <c r="E106" s="57">
+      <c r="E106" s="69">
         <f t="shared" si="9"/>
         <v>10.149253731343284</v>
       </c>
-      <c r="F106" s="58"/>
+      <c r="F106" s="70"/>
       <c r="I106" s="18">
         <f t="shared" si="7"/>
         <v>1.0000000000000001E-5</v>
@@ -20729,11 +20737,11 @@
         <v>25</v>
       </c>
       <c r="D107" s="33"/>
-      <c r="E107" s="57">
+      <c r="E107" s="69">
         <f t="shared" si="9"/>
         <v>24.427860696517413</v>
       </c>
-      <c r="F107" s="58"/>
+      <c r="F107" s="70"/>
       <c r="I107" s="19">
         <f t="shared" si="7"/>
         <v>2.5000000000000001E-5</v>
@@ -20756,11 +20764,11 @@
         <v>50</v>
       </c>
       <c r="D108" s="15"/>
-      <c r="E108" s="60">
+      <c r="E108" s="72">
         <f t="shared" si="9"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F108" s="61"/>
+      <c r="F108" s="73"/>
       <c r="I108" s="18">
         <f t="shared" si="7"/>
         <v>5.0000000000000002E-5</v>
@@ -20781,13 +20789,13 @@
       <c r="B109" s="9">
         <v>0</v>
       </c>
-      <c r="C109" s="72"/>
-      <c r="D109" s="73"/>
-      <c r="E109" s="74">
+      <c r="C109" s="84"/>
+      <c r="D109" s="85"/>
+      <c r="E109" s="86">
         <f t="shared" ref="E109" si="11">(B109+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F109" s="75"/>
+      <c r="F109" s="87"/>
       <c r="I109" s="18">
         <f>E109/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -20808,13 +20816,13 @@
       <c r="B110" s="6">
         <v>0</v>
       </c>
-      <c r="C110" s="48"/>
-      <c r="D110" s="56"/>
-      <c r="E110" s="57">
+      <c r="C110" s="60"/>
+      <c r="D110" s="68"/>
+      <c r="E110" s="69">
         <f t="shared" ref="E110:E117" si="12">(B110+0.001)/0.0201</f>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F110" s="58"/>
+      <c r="F110" s="70"/>
       <c r="I110" s="18">
         <f t="shared" ref="I110:I117" si="13">E110/1000000</f>
         <v>4.9751243781094531E-8</v>
@@ -20835,13 +20843,13 @@
       <c r="B111" s="6">
         <v>0</v>
       </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="57">
+      <c r="C111" s="60"/>
+      <c r="D111" s="68"/>
+      <c r="E111" s="69">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F111" s="58"/>
+      <c r="F111" s="70"/>
       <c r="I111" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20862,13 +20870,13 @@
       <c r="B112" s="6">
         <v>0</v>
       </c>
-      <c r="C112" s="48"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="57">
+      <c r="C112" s="60"/>
+      <c r="D112" s="68"/>
+      <c r="E112" s="69">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F112" s="58"/>
+      <c r="F112" s="70"/>
       <c r="I112" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20889,13 +20897,13 @@
       <c r="B113" s="6">
         <v>0</v>
       </c>
-      <c r="C113" s="48"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="57">
+      <c r="C113" s="60"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="69">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F113" s="58"/>
+      <c r="F113" s="70"/>
       <c r="I113" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20916,13 +20924,13 @@
       <c r="B114" s="6">
         <v>2E-3</v>
       </c>
-      <c r="C114" s="48"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="57">
+      <c r="C114" s="60"/>
+      <c r="D114" s="68"/>
+      <c r="E114" s="69">
         <f t="shared" si="12"/>
         <v>0.1492537313432836</v>
       </c>
-      <c r="F114" s="58"/>
+      <c r="F114" s="70"/>
       <c r="I114" s="18">
         <f t="shared" si="13"/>
         <v>1.492537313432836E-7</v>
@@ -20943,13 +20951,13 @@
       <c r="B115" s="6">
         <v>0.01</v>
       </c>
-      <c r="C115" s="48"/>
-      <c r="D115" s="56"/>
-      <c r="E115" s="57">
+      <c r="C115" s="60"/>
+      <c r="D115" s="68"/>
+      <c r="E115" s="69">
         <f t="shared" si="12"/>
         <v>0.54726368159203975</v>
       </c>
-      <c r="F115" s="58"/>
+      <c r="F115" s="70"/>
       <c r="I115" s="18">
         <f t="shared" si="13"/>
         <v>5.4726368159203972E-7</v>
@@ -20970,13 +20978,13 @@
       <c r="B116" s="6">
         <v>0</v>
       </c>
-      <c r="C116" s="48"/>
-      <c r="D116" s="56"/>
-      <c r="E116" s="57">
+      <c r="C116" s="60"/>
+      <c r="D116" s="68"/>
+      <c r="E116" s="69">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F116" s="58"/>
+      <c r="F116" s="70"/>
       <c r="I116" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -20997,13 +21005,13 @@
       <c r="B117" s="8">
         <v>0</v>
       </c>
-      <c r="C117" s="52"/>
-      <c r="D117" s="59"/>
-      <c r="E117" s="60">
+      <c r="C117" s="64"/>
+      <c r="D117" s="71"/>
+      <c r="E117" s="72">
         <f t="shared" si="12"/>
         <v>4.975124378109453E-2</v>
       </c>
-      <c r="F117" s="61"/>
+      <c r="F117" s="73"/>
       <c r="I117" s="18">
         <f t="shared" si="13"/>
         <v>4.9751243781094531E-8</v>
@@ -21019,7 +21027,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I120" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K120">
         <v>62.005400000000002</v>
@@ -21035,16 +21043,16 @@
       </c>
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="70" t="s">
+      <c r="A122" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="B122" s="70"/>
-      <c r="C122" s="70"/>
-      <c r="D122" s="70"/>
-      <c r="E122" s="70"/>
-      <c r="F122" s="70"/>
-      <c r="G122" s="70"/>
-      <c r="H122" s="70"/>
+      <c r="B122" s="82"/>
+      <c r="C122" s="82"/>
+      <c r="D122" s="82"/>
+      <c r="E122" s="82"/>
+      <c r="F122" s="82"/>
+      <c r="G122" s="82"/>
+      <c r="H122" s="82"/>
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I123" s="16" t="s">
@@ -21088,14 +21096,14 @@
         <v>56</v>
       </c>
       <c r="B125" s="4"/>
-      <c r="C125" s="62">
+      <c r="C125" s="74">
         <v>2.5</v>
       </c>
-      <c r="D125" s="63"/>
-      <c r="E125" s="68">
+      <c r="D125" s="75"/>
+      <c r="E125" s="80">
         <v>0</v>
       </c>
-      <c r="F125" s="69"/>
+      <c r="F125" s="81"/>
       <c r="G125" s="35"/>
       <c r="I125" s="16">
         <f t="shared" ref="I125:I132" si="16">C125/1000000</f>
@@ -21115,15 +21123,15 @@
         <v>11</v>
       </c>
       <c r="B126" s="2"/>
-      <c r="C126" s="66">
+      <c r="C126" s="78">
         <v>5</v>
       </c>
-      <c r="D126" s="67"/>
-      <c r="E126" s="50">
+      <c r="D126" s="79"/>
+      <c r="E126" s="62">
         <f>(B126-0.0011)/0.0019</f>
         <v>-0.57894736842105265</v>
       </c>
-      <c r="F126" s="51"/>
+      <c r="F126" s="63"/>
       <c r="G126" s="35"/>
       <c r="I126" s="18">
         <f t="shared" si="16"/>
@@ -21145,15 +21153,15 @@
       <c r="B127" s="6">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="C127" s="48">
+      <c r="C127" s="60">
         <v>10</v>
       </c>
-      <c r="D127" s="49"/>
-      <c r="E127" s="50">
+      <c r="D127" s="61"/>
+      <c r="E127" s="62">
         <f t="shared" ref="E127:E141" si="18">(B127-0.0011)/0.0019</f>
         <v>11</v>
       </c>
-      <c r="F127" s="51"/>
+      <c r="F127" s="63"/>
       <c r="G127" s="35"/>
       <c r="I127" s="18">
         <f t="shared" si="16"/>
@@ -21173,15 +21181,15 @@
         <v>12</v>
       </c>
       <c r="B128" s="6"/>
-      <c r="C128" s="48">
+      <c r="C128" s="60">
         <v>25</v>
       </c>
-      <c r="D128" s="49"/>
-      <c r="E128" s="50">
+      <c r="D128" s="61"/>
+      <c r="E128" s="62">
         <f t="shared" si="18"/>
         <v>-0.57894736842105265</v>
       </c>
-      <c r="F128" s="51"/>
+      <c r="F128" s="63"/>
       <c r="G128" s="35"/>
       <c r="I128" s="18">
         <f t="shared" si="16"/>
@@ -21203,15 +21211,15 @@
       <c r="B129" s="6">
         <v>0.10199999999999999</v>
       </c>
-      <c r="C129" s="48">
+      <c r="C129" s="60">
         <v>50</v>
       </c>
-      <c r="D129" s="49"/>
-      <c r="E129" s="50">
+      <c r="D129" s="61"/>
+      <c r="E129" s="62">
         <f t="shared" si="18"/>
         <v>53.105263157894733</v>
       </c>
-      <c r="F129" s="51"/>
+      <c r="F129" s="63"/>
       <c r="G129" s="35"/>
       <c r="I129" s="18">
         <f t="shared" si="16"/>
@@ -21233,15 +21241,15 @@
       <c r="B130" s="6">
         <v>0.19400000000000001</v>
       </c>
-      <c r="C130" s="48">
+      <c r="C130" s="60">
         <v>100</v>
       </c>
-      <c r="D130" s="49"/>
-      <c r="E130" s="50">
+      <c r="D130" s="61"/>
+      <c r="E130" s="62">
         <f t="shared" si="18"/>
         <v>101.5263157894737</v>
       </c>
-      <c r="F130" s="51"/>
+      <c r="F130" s="63"/>
       <c r="G130" s="35"/>
       <c r="I130" s="18">
         <f t="shared" si="16"/>
@@ -21263,15 +21271,15 @@
       <c r="B131" s="6">
         <v>0.376</v>
       </c>
-      <c r="C131" s="48">
+      <c r="C131" s="60">
         <v>200</v>
       </c>
-      <c r="D131" s="49"/>
-      <c r="E131" s="50">
+      <c r="D131" s="61"/>
+      <c r="E131" s="62">
         <f t="shared" si="18"/>
         <v>197.31578947368422</v>
       </c>
-      <c r="F131" s="51"/>
+      <c r="F131" s="63"/>
       <c r="G131" s="35"/>
       <c r="I131" s="18">
         <f t="shared" si="16"/>
@@ -21293,15 +21301,15 @@
       <c r="B132" s="8">
         <v>0.96699999999999997</v>
       </c>
-      <c r="C132" s="52">
+      <c r="C132" s="64">
         <v>500</v>
       </c>
-      <c r="D132" s="53"/>
-      <c r="E132" s="54">
+      <c r="D132" s="65"/>
+      <c r="E132" s="66">
         <f t="shared" si="18"/>
         <v>508.36842105263156</v>
       </c>
-      <c r="F132" s="55"/>
+      <c r="F132" s="67"/>
       <c r="G132" s="35"/>
       <c r="I132" s="19">
         <f t="shared" si="16"/>
@@ -21323,13 +21331,13 @@
       <c r="B133" s="9">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C133" s="72"/>
-      <c r="D133" s="78"/>
-      <c r="E133" s="79">
+      <c r="C133" s="84"/>
+      <c r="D133" s="90"/>
+      <c r="E133" s="91">
         <f t="shared" si="18"/>
         <v>4.1578947368421044</v>
       </c>
-      <c r="F133" s="80"/>
+      <c r="F133" s="92"/>
       <c r="G133" s="35"/>
       <c r="I133" s="18">
         <f>E133/1000000</f>
@@ -21351,13 +21359,13 @@
       <c r="B134" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C134" s="48"/>
-      <c r="D134" s="49"/>
-      <c r="E134" s="50">
+      <c r="C134" s="60"/>
+      <c r="D134" s="61"/>
+      <c r="E134" s="62">
         <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F134" s="51"/>
+      <c r="F134" s="63"/>
       <c r="G134" s="35"/>
       <c r="I134" s="18">
         <f>E134/1000000</f>
@@ -21379,13 +21387,13 @@
       <c r="B135" s="6">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="C135" s="48"/>
-      <c r="D135" s="49"/>
-      <c r="E135" s="50">
+      <c r="C135" s="60"/>
+      <c r="D135" s="61"/>
+      <c r="E135" s="62">
         <f t="shared" si="18"/>
         <v>5.2105263157894735</v>
       </c>
-      <c r="F135" s="51"/>
+      <c r="F135" s="63"/>
       <c r="G135" s="35"/>
       <c r="I135" s="18">
         <f t="shared" ref="I135:I141" si="22">E135/1000000</f>
@@ -21407,13 +21415,13 @@
       <c r="B136" s="6">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="C136" s="48"/>
-      <c r="D136" s="49"/>
-      <c r="E136" s="50">
+      <c r="C136" s="60"/>
+      <c r="D136" s="61"/>
+      <c r="E136" s="62">
         <f t="shared" si="18"/>
         <v>3.1052631578947367</v>
       </c>
-      <c r="F136" s="51"/>
+      <c r="F136" s="63"/>
       <c r="G136" s="35"/>
       <c r="I136" s="18">
         <f t="shared" si="22"/>
@@ -21435,13 +21443,13 @@
       <c r="B137" s="6">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="C137" s="48"/>
-      <c r="D137" s="49"/>
-      <c r="E137" s="50">
+      <c r="C137" s="60"/>
+      <c r="D137" s="61"/>
+      <c r="E137" s="62">
         <f t="shared" si="18"/>
         <v>2.5789473684210527</v>
       </c>
-      <c r="F137" s="51"/>
+      <c r="F137" s="63"/>
       <c r="G137" s="35"/>
       <c r="I137" s="18">
         <f t="shared" si="22"/>
@@ -21463,13 +21471,13 @@
       <c r="B138" s="6">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C138" s="48"/>
-      <c r="D138" s="49"/>
-      <c r="E138" s="50">
+      <c r="C138" s="60"/>
+      <c r="D138" s="61"/>
+      <c r="E138" s="62">
         <f t="shared" si="18"/>
         <v>23.105263157894736</v>
       </c>
-      <c r="F138" s="51"/>
+      <c r="F138" s="63"/>
       <c r="G138" s="35"/>
       <c r="I138" s="18">
         <f t="shared" si="22"/>
@@ -21491,13 +21499,13 @@
       <c r="B139" s="6">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="C139" s="48"/>
-      <c r="D139" s="49"/>
-      <c r="E139" s="50">
+      <c r="C139" s="60"/>
+      <c r="D139" s="61"/>
+      <c r="E139" s="62">
         <f t="shared" si="18"/>
         <v>18.368421052631579</v>
       </c>
-      <c r="F139" s="51"/>
+      <c r="F139" s="63"/>
       <c r="G139" s="35"/>
       <c r="I139" s="18">
         <f t="shared" si="22"/>
@@ -21519,13 +21527,13 @@
       <c r="B140" s="6">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="C140" s="48"/>
-      <c r="D140" s="49"/>
-      <c r="E140" s="50">
+      <c r="C140" s="60"/>
+      <c r="D140" s="61"/>
+      <c r="E140" s="62">
         <f t="shared" si="18"/>
         <v>13.105263157894736</v>
       </c>
-      <c r="F140" s="51"/>
+      <c r="F140" s="63"/>
       <c r="G140" s="35"/>
       <c r="I140" s="18">
         <f t="shared" si="22"/>
@@ -21547,13 +21555,13 @@
       <c r="B141" s="8">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="C141" s="52"/>
-      <c r="D141" s="53"/>
-      <c r="E141" s="54">
+      <c r="C141" s="64"/>
+      <c r="D141" s="65"/>
+      <c r="E141" s="66">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
-      <c r="F141" s="55"/>
+      <c r="F141" s="67"/>
       <c r="I141" s="18">
         <f t="shared" si="22"/>
         <v>9.9999999999999995E-7</v>
@@ -21832,13 +21840,13 @@
         <f t="shared" si="0"/>
         <v>L1</v>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="95">
         <v>5.9352352258064525E-2</v>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="95">
         <v>9.6381967647058819E-3</v>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="95">
         <v>1.0997799894736842</v>
       </c>
     </row>
@@ -21856,13 +21864,13 @@
         <f t="shared" si="0"/>
         <v>L2</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="95">
         <v>1.7390627135483876</v>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="95">
         <v>3.881805852941176E-2</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="95">
         <v>1.1324144105263159</v>
       </c>
     </row>
@@ -21880,13 +21888,13 @@
         <f t="shared" si="0"/>
         <v>L3</v>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="95">
         <v>0.66645321032258065</v>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="95">
         <v>1.2290911470588233E-2</v>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="95">
         <v>0.80607019999999996</v>
       </c>
     </row>
@@ -21904,13 +21912,13 @@
         <f t="shared" si="0"/>
         <v>L4</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="95" t="s">
         <v>106</v>
       </c>
     </row>
@@ -22048,13 +22056,13 @@
         <f t="shared" si="1"/>
         <v>L1</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="95">
         <v>5.9352352258064525E-2</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="95">
         <v>9.6381967647058819E-3</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="95">
         <v>1.0997799894736842</v>
       </c>
     </row>
@@ -22072,13 +22080,13 @@
         <f t="shared" si="1"/>
         <v>L2</v>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="95">
         <v>1.7390627135483876</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="95">
         <v>3.881805852941176E-2</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="95">
         <v>1.1324144105263159</v>
       </c>
     </row>
@@ -22096,13 +22104,13 @@
         <f t="shared" si="1"/>
         <v>L3</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="95">
         <v>0.66645321032258065</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="95">
         <v>1.2290911470588233E-2</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="95">
         <v>0.80607019999999996</v>
       </c>
     </row>
@@ -22120,13 +22128,13 @@
         <f t="shared" si="1"/>
         <v>L4</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="95" t="s">
         <v>106</v>
       </c>
     </row>
@@ -22264,13 +22272,13 @@
         <f t="shared" si="2"/>
         <v>L1</v>
       </c>
-      <c r="E25" s="47">
+      <c r="E25" s="95">
         <v>0.59339017375000014</v>
       </c>
-      <c r="F25" s="47">
+      <c r="F25" s="95">
         <v>5.9843232227488148E-3</v>
       </c>
-      <c r="G25" s="47">
+      <c r="G25" s="95">
         <v>0.62984432631578957</v>
       </c>
     </row>
@@ -22288,13 +22296,13 @@
         <f t="shared" si="2"/>
         <v>L2</v>
       </c>
-      <c r="E26" s="47">
+      <c r="E26" s="95">
         <v>8.605848625000001E-2</v>
       </c>
-      <c r="F26" s="47">
+      <c r="F26" s="95">
         <v>3.4196132701421807E-2</v>
       </c>
-      <c r="G26" s="47">
+      <c r="G26" s="95">
         <v>0.59720990526315787</v>
       </c>
     </row>
@@ -22312,13 +22320,13 @@
         <f t="shared" si="2"/>
         <v>L3</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="95">
         <v>5.4115380000000005E-2</v>
       </c>
-      <c r="F27" s="47">
+      <c r="F27" s="95">
         <v>8.5490331753554482E-3</v>
       </c>
-      <c r="G27" s="47">
+      <c r="G27" s="95">
         <v>0.98882295789473695</v>
       </c>
     </row>
@@ -22336,13 +22344,13 @@
         <f t="shared" si="2"/>
         <v>L4</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="95" t="s">
         <v>106</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="95" t="s">
         <v>106</v>
       </c>
     </row>
@@ -22480,13 +22488,13 @@
         <f t="shared" si="3"/>
         <v>L1</v>
       </c>
-      <c r="E34" s="47">
+      <c r="E34" s="95">
         <v>0.19713459857142859</v>
       </c>
-      <c r="F34" s="47">
+      <c r="F34" s="95">
         <v>8.9743582089552249E-4</v>
       </c>
-      <c r="G34" s="47">
+      <c r="G34" s="95">
         <v>0.81259708421052634</v>
       </c>
     </row>
@@ -22504,13 +22512,13 @@
         <f t="shared" si="3"/>
         <v>L2</v>
       </c>
-      <c r="E35" s="47">
+      <c r="E35" s="95">
         <v>0.38856315367346944</v>
       </c>
-      <c r="F35" s="47">
+      <c r="F35" s="95">
         <v>9.8717940298507466E-3</v>
       </c>
-      <c r="G35" s="47">
+      <c r="G35" s="95">
         <v>1.138941294736842</v>
       </c>
     </row>
@@ -22528,13 +22536,13 @@
         <f t="shared" si="3"/>
         <v>L3</v>
       </c>
-      <c r="E36" s="47">
+      <c r="E36" s="95">
         <v>0.39408513122448985</v>
       </c>
-      <c r="F36" s="47">
+      <c r="F36" s="95">
         <v>2.692307462686568E-3</v>
       </c>
-      <c r="G36" s="47">
+      <c r="G36" s="95">
         <v>1.4326510842105264</v>
       </c>
     </row>
@@ -22552,415 +22560,395 @@
         <f t="shared" si="3"/>
         <v>L4</v>
       </c>
-      <c r="E37" s="47">
+      <c r="E37" s="95">
         <v>4.6200545510204097E-2</v>
       </c>
-      <c r="F37" s="47">
+      <c r="F37" s="95">
         <v>8.9743582089552249E-4</v>
       </c>
-      <c r="G37" s="47">
+      <c r="G37" s="95">
         <v>6.2005400000000002E-2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G37" xr:uid="{90F586EF-906E-4D10-BA9A-6359CCC6DFA0}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB11AC0-5135-4DD2-A5FB-6D266A3E4B2C}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A2:G26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="7" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="87" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="93" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="89" t="s">
+      <c r="F4" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="48">
+        <v>0.11294683</v>
+      </c>
+      <c r="C5" s="48">
+        <v>7.7492951000000004E-2</v>
+      </c>
+      <c r="D5" s="48">
+        <v>1.17862977E-2</v>
+      </c>
+      <c r="E5" s="48">
+        <v>7.4871069999999998E-3</v>
+      </c>
+      <c r="F5" s="48">
+        <v>0.13216940999999999</v>
+      </c>
+      <c r="G5" s="49">
+        <v>0.174820211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="48">
+        <v>0.68796553999999999</v>
+      </c>
+      <c r="C6" s="48">
+        <v>1.12860228</v>
+      </c>
+      <c r="D6" s="48">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E6" s="48">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F6" s="48">
+        <v>0.51072868999999999</v>
+      </c>
+      <c r="G6" s="49">
+        <v>0.170398352</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="53">
+        <v>0.40045619999999998</v>
+      </c>
+      <c r="C7" s="53">
+        <v>0.80183163800000001</v>
+      </c>
+      <c r="D7" s="53">
+        <v>7.1953829999999996E-3</v>
+      </c>
+      <c r="E7" s="53">
+        <v>7.0582400000000003E-3</v>
+      </c>
+      <c r="F7" s="53">
+        <v>0.32144899999999998</v>
+      </c>
+      <c r="G7" s="54">
+        <v>0.25785028199999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="55" t="s">
         <v>128</v>
       </c>
-      <c r="D3" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="90" t="s">
+      <c r="C12" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="90" t="s">
+      <c r="E12" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="56">
+        <v>3.7810209999999997E-2</v>
+      </c>
+      <c r="C13" s="56">
+        <v>6.0655305999999999E-2</v>
+      </c>
+      <c r="D13" s="56">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E13" s="56">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F13" s="56">
+        <v>9.1376379999999993E-2</v>
+      </c>
+      <c r="G13" s="57">
+        <v>0.10581473</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="B14" s="48">
+        <v>1.151371E-2</v>
+      </c>
+      <c r="C14" s="48">
+        <v>1.6578053999999998E-2</v>
+      </c>
+      <c r="D14" s="48">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E14" s="48">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F14" s="48">
+        <v>0.15664522</v>
+      </c>
+      <c r="G14" s="49">
+        <v>0.22000215300000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="48">
+        <v>1.109189E-2</v>
+      </c>
+      <c r="C15" s="48">
+        <v>1.3172427E-2</v>
+      </c>
+      <c r="D15" s="48">
+        <v>2.6044685000000001E-3</v>
+      </c>
+      <c r="E15" s="48">
+        <v>1.9957429999999999E-3</v>
+      </c>
+      <c r="F15" s="48">
+        <v>0.14032801</v>
+      </c>
+      <c r="G15" s="49">
+        <v>0.16569803899999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B16" s="53">
+        <v>2.01386E-2</v>
+      </c>
+      <c r="C16" s="53">
+        <v>3.6000381999999997E-2</v>
+      </c>
+      <c r="D16" s="53">
+        <v>2.604468E-3</v>
+      </c>
+      <c r="E16" s="53">
+        <v>1.8052179999999999E-3</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0.12944990000000001</v>
+      </c>
+      <c r="G16" s="54">
+        <v>0.15678319700000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="90" t="s">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="52" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="95">
-        <v>1</v>
-      </c>
-      <c r="B4" s="83">
-        <v>0.40045619999999998</v>
-      </c>
-      <c r="C4" s="83">
-        <v>0.80183163800000001</v>
-      </c>
-      <c r="D4" s="83">
-        <v>7.1953829999999996E-3</v>
-      </c>
-      <c r="E4" s="83">
-        <v>7.0582400000000003E-3</v>
-      </c>
-      <c r="F4" s="83">
-        <v>0.32144899999999998</v>
-      </c>
-      <c r="G4" s="84">
-        <v>0.25785028199999999</v>
-      </c>
-      <c r="H4" s="85"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="95">
-        <v>2</v>
-      </c>
-      <c r="B5" s="83">
-        <v>2.01386E-2</v>
-      </c>
-      <c r="C5" s="83">
-        <v>3.6000381999999997E-2</v>
-      </c>
-      <c r="D5" s="83">
-        <v>2.604468E-3</v>
-      </c>
-      <c r="E5" s="83">
-        <v>1.8052179999999999E-3</v>
-      </c>
-      <c r="F5" s="83">
-        <v>0.12944990000000001</v>
-      </c>
-      <c r="G5" s="84">
-        <v>0.15678319700000001</v>
-      </c>
-      <c r="H5" s="85"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="94">
-        <v>3</v>
-      </c>
-      <c r="B6" s="91">
+      <c r="G21" s="52" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="56">
+        <v>0.22730737000000001</v>
+      </c>
+      <c r="C22" s="56">
+        <v>0.25255018699999998</v>
+      </c>
+      <c r="D22" s="56">
+        <v>6.5395380999999997E-3</v>
+      </c>
+      <c r="E22" s="56">
+        <v>4.1370260000000002E-3</v>
+      </c>
+      <c r="F22" s="56">
+        <v>0.91050034999999996</v>
+      </c>
+      <c r="G22" s="57">
+        <v>0.23094473900000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="48">
+        <v>0.98818676999999999</v>
+      </c>
+      <c r="C23" s="48">
+        <v>0.87578789000000001</v>
+      </c>
+      <c r="D23" s="48">
+        <v>3.0426010900000001E-2</v>
+      </c>
+      <c r="E23" s="48">
+        <v>1.3874948E-2</v>
+      </c>
+      <c r="F23" s="48">
+        <v>1.00024501</v>
+      </c>
+      <c r="G23" s="49">
+        <v>0.26870768299999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="48">
+        <v>0.44527673000000001</v>
+      </c>
+      <c r="C24" s="48">
+        <v>0.29066925799999999</v>
+      </c>
+      <c r="D24" s="48">
+        <v>8.9557908999999998E-3</v>
+      </c>
+      <c r="E24" s="48">
+        <v>4.5329439999999997E-3</v>
+      </c>
+      <c r="F24" s="48">
+        <v>1.00840361</v>
+      </c>
+      <c r="G24" s="49">
+        <v>0.29566137100000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" s="53">
+        <v>4.620055E-2</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="53">
+        <v>8.9743579999999998E-4</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="54">
+        <v>6.2005400000000002E-2</v>
+      </c>
+      <c r="G25" s="54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="53">
         <v>0.51456029999999997</v>
       </c>
-      <c r="C6" s="91">
+      <c r="C26" s="53">
         <v>0.59243359299999998</v>
       </c>
-      <c r="D6" s="91">
+      <c r="D26" s="53">
         <v>1.4198677E-2</v>
       </c>
-      <c r="E6" s="91">
+      <c r="E26" s="53">
         <v>1.3739723000000001E-2</v>
       </c>
-      <c r="F6" s="91">
+      <c r="F26" s="53">
         <v>0.90296929999999997</v>
       </c>
-      <c r="G6" s="92">
+      <c r="G26" s="54">
         <v>0.34503958499999998</v>
       </c>
-      <c r="H6" s="85"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="85"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="85"/>
-      <c r="F8" s="85"/>
-      <c r="G8" s="85"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="87" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="93" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="89" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="89" t="s">
-        <v>132</v>
-      </c>
-      <c r="E11" s="90" t="s">
-        <v>129</v>
-      </c>
-      <c r="F11" s="90" t="s">
-        <v>133</v>
-      </c>
-      <c r="G11" s="90" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="88" t="s">
-        <v>121</v>
-      </c>
-      <c r="B12" s="83">
-        <v>0.11294683</v>
-      </c>
-      <c r="C12" s="83">
-        <v>7.7492951000000004E-2</v>
-      </c>
-      <c r="D12" s="83">
-        <v>1.17862977E-2</v>
-      </c>
-      <c r="E12" s="83">
-        <v>7.4871069999999998E-3</v>
-      </c>
-      <c r="F12" s="83">
-        <v>0.13216940999999999</v>
-      </c>
-      <c r="G12" s="84">
-        <v>0.174820211</v>
-      </c>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="88" t="s">
-        <v>122</v>
-      </c>
-      <c r="B13" s="83">
-        <v>0.68796553999999999</v>
-      </c>
-      <c r="C13" s="83">
-        <v>1.12860228</v>
-      </c>
-      <c r="D13" s="83">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="E13" s="83">
-        <v>1.9957429999999999E-3</v>
-      </c>
-      <c r="F13" s="83">
-        <v>0.51072868999999999</v>
-      </c>
-      <c r="G13" s="84">
-        <v>0.170398352</v>
-      </c>
-      <c r="H13" s="85"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="88" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="83">
-        <v>3.7810209999999997E-2</v>
-      </c>
-      <c r="C14" s="83">
-        <v>6.0655305999999999E-2</v>
-      </c>
-      <c r="D14" s="83">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="E14" s="83">
-        <v>1.9957429999999999E-3</v>
-      </c>
-      <c r="F14" s="83">
-        <v>9.1376379999999993E-2</v>
-      </c>
-      <c r="G14" s="84">
-        <v>0.10581473</v>
-      </c>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="83">
-        <v>1.151371E-2</v>
-      </c>
-      <c r="C15" s="83">
-        <v>1.6578053999999998E-2</v>
-      </c>
-      <c r="D15" s="83">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="E15" s="83">
-        <v>1.9957429999999999E-3</v>
-      </c>
-      <c r="F15" s="83">
-        <v>0.15664522</v>
-      </c>
-      <c r="G15" s="84">
-        <v>0.22000215300000001</v>
-      </c>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="88" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="83">
-        <v>1.109189E-2</v>
-      </c>
-      <c r="C16" s="83">
-        <v>1.3172427E-2</v>
-      </c>
-      <c r="D16" s="83">
-        <v>2.6044685000000001E-3</v>
-      </c>
-      <c r="E16" s="83">
-        <v>1.9957429999999999E-3</v>
-      </c>
-      <c r="F16" s="83">
-        <v>0.14032801</v>
-      </c>
-      <c r="G16" s="84">
-        <v>0.16569803899999999</v>
-      </c>
-      <c r="H16" s="85"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="88" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" s="83">
-        <v>0.22730737000000001</v>
-      </c>
-      <c r="C17" s="83">
-        <v>0.25255018699999998</v>
-      </c>
-      <c r="D17" s="83">
-        <v>6.5395380999999997E-3</v>
-      </c>
-      <c r="E17" s="83">
-        <v>4.1370260000000002E-3</v>
-      </c>
-      <c r="F17" s="83">
-        <v>0.91050034999999996</v>
-      </c>
-      <c r="G17" s="84">
-        <v>0.23094473900000001</v>
-      </c>
-      <c r="H17" s="85"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="83">
-        <v>0.98818676999999999</v>
-      </c>
-      <c r="C18" s="83">
-        <v>0.87578789000000001</v>
-      </c>
-      <c r="D18" s="83">
-        <v>3.0426010900000001E-2</v>
-      </c>
-      <c r="E18" s="83">
-        <v>1.3874948E-2</v>
-      </c>
-      <c r="F18" s="83">
-        <v>1.00024501</v>
-      </c>
-      <c r="G18" s="84">
-        <v>0.26870768299999997</v>
-      </c>
-      <c r="H18" s="85"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="88" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="83">
-        <v>0.44527673000000001</v>
-      </c>
-      <c r="C19" s="83">
-        <v>0.29066925799999999</v>
-      </c>
-      <c r="D19" s="83">
-        <v>8.9557908999999998E-3</v>
-      </c>
-      <c r="E19" s="83">
-        <v>4.5329439999999997E-3</v>
-      </c>
-      <c r="F19" s="83">
-        <v>1.00840361</v>
-      </c>
-      <c r="G19" s="84">
-        <v>0.29566137100000001</v>
-      </c>
-      <c r="H19" s="85"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="91">
-        <v>4.620055E-2</v>
-      </c>
-      <c r="C20" s="91" t="s">
-        <v>106</v>
-      </c>
-      <c r="D20" s="91">
-        <v>8.9743579999999998E-4</v>
-      </c>
-      <c r="E20" s="92" t="s">
-        <v>106</v>
-      </c>
-      <c r="F20" s="92">
-        <v>6.2005400000000002E-2</v>
-      </c>
-      <c r="G20" s="92" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="85"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
